--- a/планы_2025_2026.xlsx
+++ b/планы_2025_2026.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F337"/>
+  <dimension ref="A1:F339"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="30" customWidth="1" style="11" min="1" max="1"/>
@@ -1948,510 +1948,534 @@
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1" s="11">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B132" s="9" t="n">
-        <v>795564.1</v>
-      </c>
-      <c r="C132" s="9" t="n">
-        <v>421720.28</v>
-      </c>
-      <c r="D132" s="9" t="n">
-        <v>1072600</v>
-      </c>
-      <c r="E132" s="9" t="n">
-        <v>643275.5</v>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Списания баллов</t>
+        </is>
+      </c>
+      <c r="B132">
+        <f>B131*0.05</f>
+        <v/>
+      </c>
+      <c r="C132">
+        <f>C131*0.05</f>
+        <v/>
+      </c>
+      <c r="D132">
+        <f>D131*0.05</f>
+        <v/>
+      </c>
+      <c r="E132">
+        <f>E131*0.05</f>
+        <v/>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1" s="11">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B133" s="9" t="n">
-        <v>1045</v>
-      </c>
-      <c r="C133" s="10" t="n">
-        <v>690</v>
-      </c>
-      <c r="D133" s="10" t="n">
-        <v>930</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>710</v>
+        <v>795564.1</v>
+      </c>
+      <c r="C133" s="9" t="n">
+        <v>421720.28</v>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>1072600</v>
+      </c>
+      <c r="E133" s="9" t="n">
+        <v>643275.5</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1" s="11">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B134" s="9" t="n">
-        <v>1150</v>
+        <v>1045</v>
       </c>
       <c r="C134" s="10" t="n">
-        <v>950</v>
-      </c>
-      <c r="D134" s="9" t="n">
-        <v>1730</v>
-      </c>
-      <c r="E134" s="9" t="n">
-        <v>1355</v>
+        <v>690</v>
+      </c>
+      <c r="D134" s="10" t="n">
+        <v>930</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>710</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1" s="11">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="n">
-        <v>60</v>
+          <t>Средний чек</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="n">
+        <v>1150</v>
       </c>
       <c r="C135" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="D135" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>60</v>
+        <v>950</v>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>1355</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1" s="11">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B136" s="10" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C136" s="10" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1" s="11">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B137" s="10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C137" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D137" s="10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1" s="11">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B138" s="10" t="n">
-        <v>195.86</v>
+        <v>15</v>
       </c>
       <c r="C138" s="10" t="n">
-        <v>180.39</v>
+        <v>10</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>201.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1" s="11">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B139" s="10" t="n">
-        <v>260</v>
+        <v>195.86</v>
       </c>
       <c r="C139" s="10" t="n">
-        <v>230</v>
+        <v>180.39</v>
       </c>
       <c r="D139" s="10" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="E139" s="10" t="n">
-        <v>260</v>
+        <v>201.8</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1" s="11">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B140" s="10" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="C140" s="10" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>125</v>
+        <v>260</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>125</v>
+        <v>260</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1" s="11">
       <c r="A141" s="7" t="inlineStr">
         <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B141" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="C141" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="D141" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1" s="11">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
           <t>Наценка кухня</t>
         </is>
       </c>
-      <c r="B141" s="10" t="n">
+      <c r="B142" s="10" t="n">
         <v>160</v>
       </c>
-      <c r="C141" s="10" t="n">
+      <c r="C142" s="10" t="n">
         <v>160</v>
       </c>
-      <c r="D141" s="10" t="n">
+      <c r="D142" s="10" t="n">
         <v>170</v>
       </c>
-      <c r="E141" s="10" t="n">
+      <c r="E142" s="10" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="142" ht="15.75" customHeight="1" s="11"/>
-    <row r="143" ht="15.75" customHeight="1" s="11">
-      <c r="A143" s="13" t="inlineStr">
+    <row r="143" ht="15.75" customHeight="1" s="11"/>
+    <row r="144" ht="15.75" customHeight="1" s="11">
+      <c r="A144" s="13" t="inlineStr">
         <is>
           <t>Ноябрь 2025</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="15.75" customHeight="1" s="11">
-      <c r="A144" s="5" t="inlineStr">
+    <row r="145" ht="15.75" customHeight="1" s="11">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="B145" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
+      <c r="C145" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D145" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E145" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F144" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
-      </c>
-    </row>
-    <row r="145" ht="15.75" customHeight="1" s="11">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="n">
-        <v>1000500</v>
-      </c>
-      <c r="C145" s="9" t="n">
-        <v>825000</v>
-      </c>
-      <c r="D145" s="9" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="E145" s="9" t="n">
-        <v>951750</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1" s="11">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>Прибыль</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B146" s="9" t="n">
-        <v>662335.66</v>
+        <v>1000500</v>
       </c>
       <c r="C146" s="9" t="n">
-        <v>515769.23</v>
+        <v>825000</v>
       </c>
       <c r="D146" s="9" t="n">
-        <v>933333.33</v>
+        <v>1400000</v>
       </c>
       <c r="E146" s="9" t="n">
-        <v>637219.29</v>
+        <v>951750</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1" s="11">
-      <c r="A147" s="7" t="inlineStr">
-        <is>
-          <t>Чеки</t>
-        </is>
-      </c>
-      <c r="B147" s="10" t="n">
-        <v>870</v>
-      </c>
-      <c r="C147" s="10" t="n">
-        <v>750</v>
-      </c>
-      <c r="D147" s="10" t="n">
-        <v>800</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>705</v>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Списания баллов</t>
+        </is>
+      </c>
+      <c r="B147">
+        <f>B146*0.05</f>
+        <v/>
+      </c>
+      <c r="C147">
+        <f>C146*0.05</f>
+        <v/>
+      </c>
+      <c r="D147">
+        <f>D146*0.05</f>
+        <v/>
+      </c>
+      <c r="E147">
+        <f>E146*0.05</f>
+        <v/>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1" s="11">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B148" s="9" t="n">
-        <v>1150</v>
+        <v>662335.66</v>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1100</v>
+        <v>515769.23</v>
       </c>
       <c r="D148" s="9" t="n">
-        <v>1750</v>
+        <v>933333.33</v>
       </c>
       <c r="E148" s="9" t="n">
-        <v>1350</v>
+        <v>637219.29</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="11">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B149" s="10" t="n">
-        <v>60</v>
+        <v>870</v>
       </c>
       <c r="C149" s="10" t="n">
-        <v>60</v>
+        <v>750</v>
       </c>
       <c r="D149" s="10" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>60</v>
+        <v>705</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" s="11">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
-        </is>
-      </c>
-      <c r="B150" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="C150" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="D150" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="E150" s="10" t="n">
-        <v>24</v>
+          <t>Средний чек</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="n">
+        <v>1150</v>
+      </c>
+      <c r="C150" s="9" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="E150" s="9" t="n">
+        <v>1350</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1" s="11">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B151" s="10" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C151" s="10" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D151" s="10" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E151" s="10" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1" s="11">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B152" s="10" t="n">
-        <v>195.86</v>
+        <v>25</v>
       </c>
       <c r="C152" s="10" t="n">
-        <v>166.79</v>
+        <v>30</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>202.59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1" s="11">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B153" s="10" t="n">
-        <v>260</v>
+        <v>15</v>
       </c>
       <c r="C153" s="10" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D153" s="10" t="n">
-        <v>260</v>
+        <v>15</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>260</v>
+        <v>16</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1" s="11">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B154" s="10" t="n">
-        <v>120</v>
+        <v>195.86</v>
       </c>
       <c r="C154" s="10" t="n">
-        <v>120</v>
+        <v>166.79</v>
       </c>
       <c r="D154" s="10" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>125</v>
+        <v>202.59</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1" s="11">
       <c r="A155" s="7" t="inlineStr">
         <is>
+          <t>Наценка розлив</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="n">
+        <v>260</v>
+      </c>
+      <c r="C155" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="D155" s="10" t="n">
+        <v>260</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1" s="11">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="C156" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="D156" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" customHeight="1" s="11">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
           <t>Наценка кухня</t>
         </is>
       </c>
-      <c r="B155" s="10" t="n">
+      <c r="B157" s="10" t="n">
         <v>160</v>
       </c>
-      <c r="C155" s="10" t="n">
+      <c r="C157" s="10" t="n">
         <v>160</v>
       </c>
-      <c r="D155" s="10" t="n">
+      <c r="D157" s="10" t="n">
         <v>170</v>
       </c>
-      <c r="E155" s="10" t="n">
+      <c r="E157" s="10" t="n">
         <v>180</v>
       </c>
     </row>
-    <row r="156" ht="15.75" customHeight="1" s="11"/>
-    <row r="157" ht="15.75" customHeight="1" s="11">
-      <c r="A157" s="13" t="inlineStr">
+    <row r="158" ht="15.75" customHeight="1" s="11"/>
+    <row r="159" ht="15.75" customHeight="1" s="11">
+      <c r="A159" s="13" t="inlineStr">
         <is>
           <t>Декабрь 2025</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="15.75" customHeight="1" s="11">
-      <c r="A158" s="5" t="inlineStr">
+    <row r="160" ht="15.75" customHeight="1" s="11">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B158" s="6" t="inlineStr">
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C158" s="6" t="inlineStr">
+      <c r="C160" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="D160" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E160" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F158" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="159" ht="15.75" customHeight="1" s="11">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B159" s="10" t="n"/>
-      <c r="C159" s="10" t="n"/>
-      <c r="D159" s="10" t="n"/>
-      <c r="E159" s="10" t="n"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1" s="11">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B160" s="10" t="n"/>
-      <c r="C160" s="10" t="n"/>
-      <c r="D160" s="10" t="n"/>
-      <c r="E160" s="10" t="n"/>
     </row>
     <row r="161" ht="15.75" customHeight="1" s="11">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B161" s="10" t="n"/>
@@ -2462,7 +2486,7 @@
     <row r="162" ht="15.75" customHeight="1" s="11">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B162" s="10" t="n"/>
@@ -2473,7 +2497,7 @@
     <row r="163" ht="15.75" customHeight="1" s="11">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B163" s="10" t="n"/>
@@ -2484,7 +2508,7 @@
     <row r="164" ht="15.75" customHeight="1" s="11">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B164" s="10" t="n"/>
@@ -2495,7 +2519,7 @@
     <row r="165" ht="15.75" customHeight="1" s="11">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B165" s="10" t="n"/>
@@ -2506,7 +2530,7 @@
     <row r="166" ht="15.75" customHeight="1" s="11">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B166" s="10" t="n"/>
@@ -2517,7 +2541,7 @@
     <row r="167" ht="15.75" customHeight="1" s="11">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B167" s="10" t="n"/>
@@ -2528,7 +2552,7 @@
     <row r="168" ht="15.75" customHeight="1" s="11">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B168" s="10" t="n"/>
@@ -2539,7 +2563,7 @@
     <row r="169" ht="15.75" customHeight="1" s="11">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B169" s="10" t="n"/>
@@ -2547,72 +2571,72 @@
       <c r="D169" s="10" t="n"/>
       <c r="E169" s="10" t="n"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1" s="11"/>
+    <row r="170" ht="15.75" customHeight="1" s="11">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="n"/>
+      <c r="C170" s="10" t="n"/>
+      <c r="D170" s="10" t="n"/>
+      <c r="E170" s="10" t="n"/>
+    </row>
     <row r="171" ht="15.75" customHeight="1" s="11">
-      <c r="A171" s="13" t="inlineStr">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B171" s="10" t="n"/>
+      <c r="C171" s="10" t="n"/>
+      <c r="D171" s="10" t="n"/>
+      <c r="E171" s="10" t="n"/>
+    </row>
+    <row r="172" ht="15.75" customHeight="1" s="11"/>
+    <row r="173" ht="15.75" customHeight="1" s="11">
+      <c r="A173" s="13" t="inlineStr">
         <is>
           <t>Январь 2026</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="15.75" customHeight="1" s="11">
-      <c r="A172" s="5" t="inlineStr">
+    <row r="174" ht="15.75" customHeight="1" s="11">
+      <c r="A174" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B172" s="6" t="inlineStr">
+      <c r="B174" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C172" s="6" t="inlineStr">
+      <c r="C174" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D174" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="E174" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="173" ht="15.75" customHeight="1" s="11">
-      <c r="A173" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B173" s="10" t="n"/>
-      <c r="C173" s="10" t="n"/>
-      <c r="D173" s="10" t="n"/>
-      <c r="E173" s="10" t="n"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1" s="11">
-      <c r="A174" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B174" s="10" t="n"/>
-      <c r="C174" s="10" t="n"/>
-      <c r="D174" s="10" t="n"/>
-      <c r="E174" s="10" t="n"/>
     </row>
     <row r="175" ht="15.75" customHeight="1" s="11">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B175" s="10" t="n"/>
@@ -2623,7 +2647,7 @@
     <row r="176" ht="15.75" customHeight="1" s="11">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B176" s="10" t="n"/>
@@ -2634,7 +2658,7 @@
     <row r="177" ht="15.75" customHeight="1" s="11">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B177" s="10" t="n"/>
@@ -2645,7 +2669,7 @@
     <row r="178" ht="15.75" customHeight="1" s="11">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B178" s="10" t="n"/>
@@ -2656,7 +2680,7 @@
     <row r="179" ht="15.75" customHeight="1" s="11">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B179" s="10" t="n"/>
@@ -2667,7 +2691,7 @@
     <row r="180" ht="15.75" customHeight="1" s="11">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B180" s="10" t="n"/>
@@ -2678,7 +2702,7 @@
     <row r="181" ht="15.75" customHeight="1" s="11">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B181" s="10" t="n"/>
@@ -2689,7 +2713,7 @@
     <row r="182" ht="15.75" customHeight="1" s="11">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B182" s="10" t="n"/>
@@ -2700,7 +2724,7 @@
     <row r="183" ht="15.75" customHeight="1" s="11">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B183" s="10" t="n"/>
@@ -2708,72 +2732,72 @@
       <c r="D183" s="10" t="n"/>
       <c r="E183" s="10" t="n"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1" s="11"/>
+    <row r="184" ht="15.75" customHeight="1" s="11">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B184" s="10" t="n"/>
+      <c r="C184" s="10" t="n"/>
+      <c r="D184" s="10" t="n"/>
+      <c r="E184" s="10" t="n"/>
+    </row>
     <row r="185" ht="15.75" customHeight="1" s="11">
-      <c r="A185" s="13" t="inlineStr">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B185" s="10" t="n"/>
+      <c r="C185" s="10" t="n"/>
+      <c r="D185" s="10" t="n"/>
+      <c r="E185" s="10" t="n"/>
+    </row>
+    <row r="186" ht="15.75" customHeight="1" s="11"/>
+    <row r="187" ht="15.75" customHeight="1" s="11">
+      <c r="A187" s="13" t="inlineStr">
         <is>
           <t>Февраль 2026</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="15.75" customHeight="1" s="11">
-      <c r="A186" s="5" t="inlineStr">
+    <row r="188" ht="15.75" customHeight="1" s="11">
+      <c r="A188" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="187" ht="15.75" customHeight="1" s="11">
-      <c r="A187" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B187" s="10" t="n"/>
-      <c r="C187" s="10" t="n"/>
-      <c r="D187" s="10" t="n"/>
-      <c r="E187" s="10" t="n"/>
-    </row>
-    <row r="188" ht="15.75" customHeight="1" s="11">
-      <c r="A188" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B188" s="10" t="n"/>
-      <c r="C188" s="10" t="n"/>
-      <c r="D188" s="10" t="n"/>
-      <c r="E188" s="10" t="n"/>
     </row>
     <row r="189" ht="15.75" customHeight="1" s="11">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B189" s="10" t="n"/>
@@ -2784,7 +2808,7 @@
     <row r="190" ht="15.75" customHeight="1" s="11">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B190" s="10" t="n"/>
@@ -2795,7 +2819,7 @@
     <row r="191" ht="15.75" customHeight="1" s="11">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B191" s="10" t="n"/>
@@ -2806,7 +2830,7 @@
     <row r="192" ht="15.75" customHeight="1" s="11">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B192" s="10" t="n"/>
@@ -2817,7 +2841,7 @@
     <row r="193" ht="15.75" customHeight="1" s="11">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B193" s="10" t="n"/>
@@ -2828,7 +2852,7 @@
     <row r="194" ht="15.75" customHeight="1" s="11">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B194" s="10" t="n"/>
@@ -2839,7 +2863,7 @@
     <row r="195" ht="15.75" customHeight="1" s="11">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B195" s="10" t="n"/>
@@ -2850,7 +2874,7 @@
     <row r="196" ht="15.75" customHeight="1" s="11">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B196" s="10" t="n"/>
@@ -2861,7 +2885,7 @@
     <row r="197" ht="15.75" customHeight="1" s="11">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B197" s="10" t="n"/>
@@ -2869,72 +2893,72 @@
       <c r="D197" s="10" t="n"/>
       <c r="E197" s="10" t="n"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1" s="11"/>
+    <row r="198" ht="15.75" customHeight="1" s="11">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B198" s="10" t="n"/>
+      <c r="C198" s="10" t="n"/>
+      <c r="D198" s="10" t="n"/>
+      <c r="E198" s="10" t="n"/>
+    </row>
     <row r="199" ht="15.75" customHeight="1" s="11">
-      <c r="A199" s="13" t="inlineStr">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B199" s="10" t="n"/>
+      <c r="C199" s="10" t="n"/>
+      <c r="D199" s="10" t="n"/>
+      <c r="E199" s="10" t="n"/>
+    </row>
+    <row r="200" ht="15.75" customHeight="1" s="11"/>
+    <row r="201" ht="15.75" customHeight="1" s="11">
+      <c r="A201" s="13" t="inlineStr">
         <is>
           <t>Март 2026</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="15.75" customHeight="1" s="11">
-      <c r="A200" s="5" t="inlineStr">
+    <row r="202" ht="15.75" customHeight="1" s="11">
+      <c r="A202" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B200" s="6" t="inlineStr">
+      <c r="B202" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C200" s="6" t="inlineStr">
+      <c r="C202" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D200" s="6" t="inlineStr">
+      <c r="D202" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E202" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F200" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="201" ht="15.75" customHeight="1" s="11">
-      <c r="A201" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B201" s="10" t="n"/>
-      <c r="C201" s="10" t="n"/>
-      <c r="D201" s="10" t="n"/>
-      <c r="E201" s="10" t="n"/>
-    </row>
-    <row r="202" ht="15.75" customHeight="1" s="11">
-      <c r="A202" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B202" s="10" t="n"/>
-      <c r="C202" s="10" t="n"/>
-      <c r="D202" s="10" t="n"/>
-      <c r="E202" s="10" t="n"/>
     </row>
     <row r="203" ht="15.75" customHeight="1" s="11">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B203" s="10" t="n"/>
@@ -2945,7 +2969,7 @@
     <row r="204" ht="15.75" customHeight="1" s="11">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B204" s="10" t="n"/>
@@ -2956,7 +2980,7 @@
     <row r="205" ht="15.75" customHeight="1" s="11">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B205" s="10" t="n"/>
@@ -2967,7 +2991,7 @@
     <row r="206" ht="15.75" customHeight="1" s="11">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B206" s="10" t="n"/>
@@ -2978,7 +3002,7 @@
     <row r="207" ht="15.75" customHeight="1" s="11">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B207" s="10" t="n"/>
@@ -2989,7 +3013,7 @@
     <row r="208" ht="15.75" customHeight="1" s="11">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B208" s="10" t="n"/>
@@ -3000,7 +3024,7 @@
     <row r="209" ht="15.75" customHeight="1" s="11">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B209" s="10" t="n"/>
@@ -3011,7 +3035,7 @@
     <row r="210" ht="15.75" customHeight="1" s="11">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B210" s="10" t="n"/>
@@ -3022,7 +3046,7 @@
     <row r="211" ht="15.75" customHeight="1" s="11">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B211" s="10" t="n"/>
@@ -3030,72 +3054,72 @@
       <c r="D211" s="10" t="n"/>
       <c r="E211" s="10" t="n"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1" s="11"/>
+    <row r="212" ht="15.75" customHeight="1" s="11">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B212" s="10" t="n"/>
+      <c r="C212" s="10" t="n"/>
+      <c r="D212" s="10" t="n"/>
+      <c r="E212" s="10" t="n"/>
+    </row>
     <row r="213" ht="15.75" customHeight="1" s="11">
-      <c r="A213" s="13" t="inlineStr">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B213" s="10" t="n"/>
+      <c r="C213" s="10" t="n"/>
+      <c r="D213" s="10" t="n"/>
+      <c r="E213" s="10" t="n"/>
+    </row>
+    <row r="214" ht="15.75" customHeight="1" s="11"/>
+    <row r="215" ht="15.75" customHeight="1" s="11">
+      <c r="A215" s="13" t="inlineStr">
         <is>
           <t>Апрель 2026</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="15.75" customHeight="1" s="11">
-      <c r="A214" s="5" t="inlineStr">
+    <row r="216" ht="15.75" customHeight="1" s="11">
+      <c r="A216" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E216" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="215" ht="15.75" customHeight="1" s="11">
-      <c r="A215" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B215" s="10" t="n"/>
-      <c r="C215" s="10" t="n"/>
-      <c r="D215" s="10" t="n"/>
-      <c r="E215" s="10" t="n"/>
-    </row>
-    <row r="216" ht="15.75" customHeight="1" s="11">
-      <c r="A216" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B216" s="10" t="n"/>
-      <c r="C216" s="10" t="n"/>
-      <c r="D216" s="10" t="n"/>
-      <c r="E216" s="10" t="n"/>
     </row>
     <row r="217" ht="15.75" customHeight="1" s="11">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B217" s="10" t="n"/>
@@ -3106,7 +3130,7 @@
     <row r="218" ht="15.75" customHeight="1" s="11">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B218" s="10" t="n"/>
@@ -3117,7 +3141,7 @@
     <row r="219" ht="15.75" customHeight="1" s="11">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B219" s="10" t="n"/>
@@ -3128,7 +3152,7 @@
     <row r="220" ht="15.75" customHeight="1" s="11">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B220" s="10" t="n"/>
@@ -3139,7 +3163,7 @@
     <row r="221" ht="15.75" customHeight="1" s="11">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B221" s="10" t="n"/>
@@ -3150,7 +3174,7 @@
     <row r="222" ht="15.75" customHeight="1" s="11">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B222" s="10" t="n"/>
@@ -3161,7 +3185,7 @@
     <row r="223" ht="15.75" customHeight="1" s="11">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B223" s="10" t="n"/>
@@ -3172,7 +3196,7 @@
     <row r="224" ht="15.75" customHeight="1" s="11">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B224" s="10" t="n"/>
@@ -3183,7 +3207,7 @@
     <row r="225" ht="15.75" customHeight="1" s="11">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B225" s="10" t="n"/>
@@ -3191,72 +3215,72 @@
       <c r="D225" s="10" t="n"/>
       <c r="E225" s="10" t="n"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1" s="11"/>
+    <row r="226" ht="15.75" customHeight="1" s="11">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B226" s="10" t="n"/>
+      <c r="C226" s="10" t="n"/>
+      <c r="D226" s="10" t="n"/>
+      <c r="E226" s="10" t="n"/>
+    </row>
     <row r="227" ht="15.75" customHeight="1" s="11">
-      <c r="A227" s="13" t="inlineStr">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B227" s="10" t="n"/>
+      <c r="C227" s="10" t="n"/>
+      <c r="D227" s="10" t="n"/>
+      <c r="E227" s="10" t="n"/>
+    </row>
+    <row r="228" ht="15.75" customHeight="1" s="11"/>
+    <row r="229" ht="15.75" customHeight="1" s="11">
+      <c r="A229" s="13" t="inlineStr">
         <is>
           <t>Май 2026</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="15.75" customHeight="1" s="11">
-      <c r="A228" s="5" t="inlineStr">
+    <row r="230" ht="15.75" customHeight="1" s="11">
+      <c r="A230" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B228" s="6" t="inlineStr">
+      <c r="B230" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C228" s="6" t="inlineStr">
+      <c r="C230" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D228" s="6" t="inlineStr">
+      <c r="D230" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="E230" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F228" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="229" ht="15.75" customHeight="1" s="11">
-      <c r="A229" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B229" s="10" t="n"/>
-      <c r="C229" s="10" t="n"/>
-      <c r="D229" s="10" t="n"/>
-      <c r="E229" s="10" t="n"/>
-    </row>
-    <row r="230" ht="15.75" customHeight="1" s="11">
-      <c r="A230" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B230" s="10" t="n"/>
-      <c r="C230" s="10" t="n"/>
-      <c r="D230" s="10" t="n"/>
-      <c r="E230" s="10" t="n"/>
     </row>
     <row r="231" ht="15.75" customHeight="1" s="11">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B231" s="10" t="n"/>
@@ -3267,7 +3291,7 @@
     <row r="232" ht="15.75" customHeight="1" s="11">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B232" s="10" t="n"/>
@@ -3278,7 +3302,7 @@
     <row r="233" ht="15.75" customHeight="1" s="11">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B233" s="10" t="n"/>
@@ -3289,7 +3313,7 @@
     <row r="234" ht="15.75" customHeight="1" s="11">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B234" s="10" t="n"/>
@@ -3300,7 +3324,7 @@
     <row r="235" ht="15.75" customHeight="1" s="11">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B235" s="10" t="n"/>
@@ -3311,7 +3335,7 @@
     <row r="236" ht="15.75" customHeight="1" s="11">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B236" s="10" t="n"/>
@@ -3322,7 +3346,7 @@
     <row r="237" ht="15.75" customHeight="1" s="11">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B237" s="10" t="n"/>
@@ -3333,7 +3357,7 @@
     <row r="238" ht="15.75" customHeight="1" s="11">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B238" s="10" t="n"/>
@@ -3344,7 +3368,7 @@
     <row r="239" ht="15.75" customHeight="1" s="11">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B239" s="10" t="n"/>
@@ -3352,72 +3376,72 @@
       <c r="D239" s="10" t="n"/>
       <c r="E239" s="10" t="n"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1" s="11"/>
+    <row r="240" ht="15.75" customHeight="1" s="11">
+      <c r="A240" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B240" s="10" t="n"/>
+      <c r="C240" s="10" t="n"/>
+      <c r="D240" s="10" t="n"/>
+      <c r="E240" s="10" t="n"/>
+    </row>
     <row r="241" ht="15.75" customHeight="1" s="11">
-      <c r="A241" s="13" t="inlineStr">
+      <c r="A241" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B241" s="10" t="n"/>
+      <c r="C241" s="10" t="n"/>
+      <c r="D241" s="10" t="n"/>
+      <c r="E241" s="10" t="n"/>
+    </row>
+    <row r="242" ht="15.75" customHeight="1" s="11"/>
+    <row r="243" ht="15.75" customHeight="1" s="11">
+      <c r="A243" s="13" t="inlineStr">
         <is>
           <t>Июнь 2026</t>
         </is>
       </c>
     </row>
-    <row r="242" ht="15.75" customHeight="1" s="11">
-      <c r="A242" s="5" t="inlineStr">
+    <row r="244" ht="15.75" customHeight="1" s="11">
+      <c r="A244" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
+      <c r="C244" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D242" s="6" t="inlineStr">
+      <c r="D244" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E244" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="243" ht="15.75" customHeight="1" s="11">
-      <c r="A243" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B243" s="10" t="n"/>
-      <c r="C243" s="10" t="n"/>
-      <c r="D243" s="10" t="n"/>
-      <c r="E243" s="10" t="n"/>
-    </row>
-    <row r="244" ht="15.75" customHeight="1" s="11">
-      <c r="A244" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B244" s="10" t="n"/>
-      <c r="C244" s="10" t="n"/>
-      <c r="D244" s="10" t="n"/>
-      <c r="E244" s="10" t="n"/>
     </row>
     <row r="245" ht="15.75" customHeight="1" s="11">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B245" s="10" t="n"/>
@@ -3428,7 +3452,7 @@
     <row r="246" ht="15.75" customHeight="1" s="11">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B246" s="10" t="n"/>
@@ -3439,7 +3463,7 @@
     <row r="247" ht="15.75" customHeight="1" s="11">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B247" s="10" t="n"/>
@@ -3450,7 +3474,7 @@
     <row r="248" ht="15.75" customHeight="1" s="11">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B248" s="10" t="n"/>
@@ -3461,7 +3485,7 @@
     <row r="249" ht="15.75" customHeight="1" s="11">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B249" s="10" t="n"/>
@@ -3472,7 +3496,7 @@
     <row r="250" ht="15.75" customHeight="1" s="11">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B250" s="10" t="n"/>
@@ -3483,7 +3507,7 @@
     <row r="251" ht="15.75" customHeight="1" s="11">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B251" s="10" t="n"/>
@@ -3494,7 +3518,7 @@
     <row r="252" ht="15.75" customHeight="1" s="11">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B252" s="10" t="n"/>
@@ -3505,7 +3529,7 @@
     <row r="253" ht="15.75" customHeight="1" s="11">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B253" s="10" t="n"/>
@@ -3513,72 +3537,72 @@
       <c r="D253" s="10" t="n"/>
       <c r="E253" s="10" t="n"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1" s="11"/>
+    <row r="254" ht="15.75" customHeight="1" s="11">
+      <c r="A254" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B254" s="10" t="n"/>
+      <c r="C254" s="10" t="n"/>
+      <c r="D254" s="10" t="n"/>
+      <c r="E254" s="10" t="n"/>
+    </row>
     <row r="255" ht="15.75" customHeight="1" s="11">
-      <c r="A255" s="13" t="inlineStr">
+      <c r="A255" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B255" s="10" t="n"/>
+      <c r="C255" s="10" t="n"/>
+      <c r="D255" s="10" t="n"/>
+      <c r="E255" s="10" t="n"/>
+    </row>
+    <row r="256" ht="15.75" customHeight="1" s="11"/>
+    <row r="257" ht="15.75" customHeight="1" s="11">
+      <c r="A257" s="13" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
     </row>
-    <row r="256" ht="15.75" customHeight="1" s="11">
-      <c r="A256" s="5" t="inlineStr">
+    <row r="258" ht="15.75" customHeight="1" s="11">
+      <c r="A258" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B256" s="6" t="inlineStr">
+      <c r="B258" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C256" s="6" t="inlineStr">
+      <c r="C258" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D256" s="6" t="inlineStr">
+      <c r="D258" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="E258" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F256" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="257" ht="15.75" customHeight="1" s="11">
-      <c r="A257" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B257" s="10" t="n"/>
-      <c r="C257" s="10" t="n"/>
-      <c r="D257" s="10" t="n"/>
-      <c r="E257" s="10" t="n"/>
-    </row>
-    <row r="258" ht="15.75" customHeight="1" s="11">
-      <c r="A258" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B258" s="10" t="n"/>
-      <c r="C258" s="10" t="n"/>
-      <c r="D258" s="10" t="n"/>
-      <c r="E258" s="10" t="n"/>
     </row>
     <row r="259" ht="15.75" customHeight="1" s="11">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B259" s="10" t="n"/>
@@ -3589,7 +3613,7 @@
     <row r="260" ht="15.75" customHeight="1" s="11">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B260" s="10" t="n"/>
@@ -3600,7 +3624,7 @@
     <row r="261" ht="15.75" customHeight="1" s="11">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B261" s="10" t="n"/>
@@ -3611,7 +3635,7 @@
     <row r="262" ht="15.75" customHeight="1" s="11">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B262" s="10" t="n"/>
@@ -3622,7 +3646,7 @@
     <row r="263" ht="15.75" customHeight="1" s="11">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B263" s="10" t="n"/>
@@ -3633,7 +3657,7 @@
     <row r="264" ht="15.75" customHeight="1" s="11">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B264" s="10" t="n"/>
@@ -3644,7 +3668,7 @@
     <row r="265" ht="15.75" customHeight="1" s="11">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B265" s="10" t="n"/>
@@ -3655,7 +3679,7 @@
     <row r="266" ht="15.75" customHeight="1" s="11">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B266" s="10" t="n"/>
@@ -3666,7 +3690,7 @@
     <row r="267" ht="15.75" customHeight="1" s="11">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B267" s="10" t="n"/>
@@ -3674,72 +3698,72 @@
       <c r="D267" s="10" t="n"/>
       <c r="E267" s="10" t="n"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1" s="11"/>
+    <row r="268" ht="15.75" customHeight="1" s="11">
+      <c r="A268" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B268" s="10" t="n"/>
+      <c r="C268" s="10" t="n"/>
+      <c r="D268" s="10" t="n"/>
+      <c r="E268" s="10" t="n"/>
+    </row>
     <row r="269" ht="15.75" customHeight="1" s="11">
-      <c r="A269" s="13" t="inlineStr">
+      <c r="A269" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B269" s="10" t="n"/>
+      <c r="C269" s="10" t="n"/>
+      <c r="D269" s="10" t="n"/>
+      <c r="E269" s="10" t="n"/>
+    </row>
+    <row r="270" ht="15.75" customHeight="1" s="11"/>
+    <row r="271" ht="15.75" customHeight="1" s="11">
+      <c r="A271" s="13" t="inlineStr">
         <is>
           <t>Август 2026</t>
         </is>
       </c>
     </row>
-    <row r="270" ht="15.75" customHeight="1" s="11">
-      <c r="A270" s="5" t="inlineStr">
+    <row r="272" ht="15.75" customHeight="1" s="11">
+      <c r="A272" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="B272" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
+      <c r="C272" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D270" s="6" t="inlineStr">
+      <c r="D272" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E272" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="271" ht="15.75" customHeight="1" s="11">
-      <c r="A271" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B271" s="10" t="n"/>
-      <c r="C271" s="10" t="n"/>
-      <c r="D271" s="10" t="n"/>
-      <c r="E271" s="10" t="n"/>
-    </row>
-    <row r="272" ht="15.75" customHeight="1" s="11">
-      <c r="A272" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B272" s="10" t="n"/>
-      <c r="C272" s="10" t="n"/>
-      <c r="D272" s="10" t="n"/>
-      <c r="E272" s="10" t="n"/>
     </row>
     <row r="273" ht="15.75" customHeight="1" s="11">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B273" s="10" t="n"/>
@@ -3750,7 +3774,7 @@
     <row r="274" ht="15.75" customHeight="1" s="11">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B274" s="10" t="n"/>
@@ -3761,7 +3785,7 @@
     <row r="275" ht="15.75" customHeight="1" s="11">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B275" s="10" t="n"/>
@@ -3772,7 +3796,7 @@
     <row r="276" ht="15.75" customHeight="1" s="11">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B276" s="10" t="n"/>
@@ -3783,7 +3807,7 @@
     <row r="277" ht="15.75" customHeight="1" s="11">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B277" s="10" t="n"/>
@@ -3794,7 +3818,7 @@
     <row r="278" ht="15.75" customHeight="1" s="11">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B278" s="10" t="n"/>
@@ -3805,7 +3829,7 @@
     <row r="279" ht="15.75" customHeight="1" s="11">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B279" s="10" t="n"/>
@@ -3816,7 +3840,7 @@
     <row r="280" ht="15.75" customHeight="1" s="11">
       <c r="A280" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B280" s="10" t="n"/>
@@ -3827,7 +3851,7 @@
     <row r="281" ht="15.75" customHeight="1" s="11">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B281" s="10" t="n"/>
@@ -3835,72 +3859,72 @@
       <c r="D281" s="10" t="n"/>
       <c r="E281" s="10" t="n"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1" s="11"/>
+    <row r="282" ht="15.75" customHeight="1" s="11">
+      <c r="A282" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B282" s="10" t="n"/>
+      <c r="C282" s="10" t="n"/>
+      <c r="D282" s="10" t="n"/>
+      <c r="E282" s="10" t="n"/>
+    </row>
     <row r="283" ht="15.75" customHeight="1" s="11">
-      <c r="A283" s="13" t="inlineStr">
+      <c r="A283" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B283" s="10" t="n"/>
+      <c r="C283" s="10" t="n"/>
+      <c r="D283" s="10" t="n"/>
+      <c r="E283" s="10" t="n"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1" s="11"/>
+    <row r="285" ht="15.75" customHeight="1" s="11">
+      <c r="A285" s="13" t="inlineStr">
         <is>
           <t>Сентябрь 2026</t>
         </is>
       </c>
     </row>
-    <row r="284" ht="15.75" customHeight="1" s="11">
-      <c r="A284" s="5" t="inlineStr">
+    <row r="286" ht="15.75" customHeight="1" s="11">
+      <c r="A286" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B284" s="6" t="inlineStr">
+      <c r="B286" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C284" s="6" t="inlineStr">
+      <c r="C286" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D284" s="6" t="inlineStr">
+      <c r="D286" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="E286" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F284" s="6" t="inlineStr">
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="285" ht="15.75" customHeight="1" s="11">
-      <c r="A285" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B285" s="10" t="n"/>
-      <c r="C285" s="10" t="n"/>
-      <c r="D285" s="10" t="n"/>
-      <c r="E285" s="10" t="n"/>
-    </row>
-    <row r="286" ht="15.75" customHeight="1" s="11">
-      <c r="A286" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B286" s="10" t="n"/>
-      <c r="C286" s="10" t="n"/>
-      <c r="D286" s="10" t="n"/>
-      <c r="E286" s="10" t="n"/>
     </row>
     <row r="287" ht="15.75" customHeight="1" s="11">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B287" s="10" t="n"/>
@@ -3911,7 +3935,7 @@
     <row r="288" ht="15.75" customHeight="1" s="11">
       <c r="A288" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B288" s="10" t="n"/>
@@ -3922,7 +3946,7 @@
     <row r="289" ht="15.75" customHeight="1" s="11">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B289" s="10" t="n"/>
@@ -3933,7 +3957,7 @@
     <row r="290" ht="15.75" customHeight="1" s="11">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B290" s="10" t="n"/>
@@ -3944,7 +3968,7 @@
     <row r="291" ht="15.75" customHeight="1" s="11">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B291" s="10" t="n"/>
@@ -3955,7 +3979,7 @@
     <row r="292" ht="15.75" customHeight="1" s="11">
       <c r="A292" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B292" s="10" t="n"/>
@@ -3966,7 +3990,7 @@
     <row r="293" ht="15.75" customHeight="1" s="11">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B293" s="10" t="n"/>
@@ -3977,7 +4001,7 @@
     <row r="294" ht="15.75" customHeight="1" s="11">
       <c r="A294" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B294" s="10" t="n"/>
@@ -3988,7 +4012,7 @@
     <row r="295" ht="15.75" customHeight="1" s="11">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B295" s="10" t="n"/>
@@ -3996,72 +4020,72 @@
       <c r="D295" s="10" t="n"/>
       <c r="E295" s="10" t="n"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1" s="11"/>
+    <row r="296" ht="15.75" customHeight="1" s="11">
+      <c r="A296" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B296" s="10" t="n"/>
+      <c r="C296" s="10" t="n"/>
+      <c r="D296" s="10" t="n"/>
+      <c r="E296" s="10" t="n"/>
+    </row>
     <row r="297" ht="15.75" customHeight="1" s="11">
-      <c r="A297" s="13" t="inlineStr">
+      <c r="A297" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B297" s="10" t="n"/>
+      <c r="C297" s="10" t="n"/>
+      <c r="D297" s="10" t="n"/>
+      <c r="E297" s="10" t="n"/>
+    </row>
+    <row r="298" ht="15.75" customHeight="1" s="11"/>
+    <row r="299" ht="15.75" customHeight="1" s="11">
+      <c r="A299" s="13" t="inlineStr">
         <is>
           <t>Октябрь 2026</t>
         </is>
       </c>
     </row>
-    <row r="298" ht="15.75" customHeight="1" s="11">
-      <c r="A298" s="5" t="inlineStr">
+    <row r="300" ht="15.75" customHeight="1" s="11">
+      <c r="A300" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B298" s="6" t="inlineStr">
+      <c r="B300" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C298" s="6" t="inlineStr">
+      <c r="C300" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D298" s="6" t="inlineStr">
+      <c r="D300" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E300" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="299" ht="15.75" customHeight="1" s="11">
-      <c r="A299" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B299" s="10" t="n"/>
-      <c r="C299" s="10" t="n"/>
-      <c r="D299" s="10" t="n"/>
-      <c r="E299" s="10" t="n"/>
-    </row>
-    <row r="300" ht="15.75" customHeight="1" s="11">
-      <c r="A300" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B300" s="10" t="n"/>
-      <c r="C300" s="10" t="n"/>
-      <c r="D300" s="10" t="n"/>
-      <c r="E300" s="10" t="n"/>
     </row>
     <row r="301" ht="15.75" customHeight="1" s="11">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B301" s="10" t="n"/>
@@ -4072,7 +4096,7 @@
     <row r="302" ht="15.75" customHeight="1" s="11">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B302" s="10" t="n"/>
@@ -4083,7 +4107,7 @@
     <row r="303" ht="15.75" customHeight="1" s="11">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B303" s="10" t="n"/>
@@ -4094,7 +4118,7 @@
     <row r="304" ht="15.75" customHeight="1" s="11">
       <c r="A304" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B304" s="10" t="n"/>
@@ -4105,7 +4129,7 @@
     <row r="305" ht="15.75" customHeight="1" s="11">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B305" s="10" t="n"/>
@@ -4116,7 +4140,7 @@
     <row r="306" ht="15.75" customHeight="1" s="11">
       <c r="A306" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B306" s="10" t="n"/>
@@ -4127,7 +4151,7 @@
     <row r="307" ht="15.75" customHeight="1" s="11">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B307" s="10" t="n"/>
@@ -4138,7 +4162,7 @@
     <row r="308" ht="15.75" customHeight="1" s="11">
       <c r="A308" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B308" s="10" t="n"/>
@@ -4149,7 +4173,7 @@
     <row r="309" ht="15.75" customHeight="1" s="11">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B309" s="10" t="n"/>
@@ -4157,72 +4181,72 @@
       <c r="D309" s="10" t="n"/>
       <c r="E309" s="10" t="n"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1" s="11"/>
+    <row r="310" ht="15.75" customHeight="1" s="11">
+      <c r="A310" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B310" s="10" t="n"/>
+      <c r="C310" s="10" t="n"/>
+      <c r="D310" s="10" t="n"/>
+      <c r="E310" s="10" t="n"/>
+    </row>
     <row r="311" ht="15.75" customHeight="1" s="11">
-      <c r="A311" s="13" t="inlineStr">
+      <c r="A311" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B311" s="10" t="n"/>
+      <c r="C311" s="10" t="n"/>
+      <c r="D311" s="10" t="n"/>
+      <c r="E311" s="10" t="n"/>
+    </row>
+    <row r="312" ht="15.75" customHeight="1" s="11"/>
+    <row r="313" ht="15.75" customHeight="1" s="11">
+      <c r="A313" s="13" t="inlineStr">
         <is>
           <t>Ноябрь 2026</t>
         </is>
       </c>
     </row>
-    <row r="312" ht="15.75" customHeight="1" s="11">
-      <c r="A312" s="5" t="inlineStr">
+    <row r="314" ht="15.75" customHeight="1" s="11">
+      <c r="A314" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B312" s="6" t="inlineStr">
+      <c r="B314" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C312" s="6" t="inlineStr">
+      <c r="C314" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D312" s="6" t="inlineStr">
+      <c r="D314" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="E314" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F312" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="313" ht="15.75" customHeight="1" s="11">
-      <c r="A313" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B313" s="10" t="n"/>
-      <c r="C313" s="10" t="n"/>
-      <c r="D313" s="10" t="n"/>
-      <c r="E313" s="10" t="n"/>
-    </row>
-    <row r="314" ht="15.75" customHeight="1" s="11">
-      <c r="A314" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B314" s="10" t="n"/>
-      <c r="C314" s="10" t="n"/>
-      <c r="D314" s="10" t="n"/>
-      <c r="E314" s="10" t="n"/>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="11">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B315" s="10" t="n"/>
@@ -4233,7 +4257,7 @@
     <row r="316" ht="15.75" customHeight="1" s="11">
       <c r="A316" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B316" s="10" t="n"/>
@@ -4244,7 +4268,7 @@
     <row r="317" ht="15.75" customHeight="1" s="11">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B317" s="10" t="n"/>
@@ -4255,7 +4279,7 @@
     <row r="318" ht="15.75" customHeight="1" s="11">
       <c r="A318" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B318" s="10" t="n"/>
@@ -4266,7 +4290,7 @@
     <row r="319" ht="15.75" customHeight="1" s="11">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B319" s="10" t="n"/>
@@ -4277,7 +4301,7 @@
     <row r="320" ht="15.75" customHeight="1" s="11">
       <c r="A320" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B320" s="10" t="n"/>
@@ -4288,7 +4312,7 @@
     <row r="321" ht="15.75" customHeight="1" s="11">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B321" s="10" t="n"/>
@@ -4299,7 +4323,7 @@
     <row r="322" ht="15.75" customHeight="1" s="11">
       <c r="A322" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B322" s="10" t="n"/>
@@ -4310,7 +4334,7 @@
     <row r="323" ht="15.75" customHeight="1" s="11">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B323" s="10" t="n"/>
@@ -4318,72 +4342,72 @@
       <c r="D323" s="10" t="n"/>
       <c r="E323" s="10" t="n"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1" s="11"/>
+    <row r="324" ht="15.75" customHeight="1" s="11">
+      <c r="A324" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B324" s="10" t="n"/>
+      <c r="C324" s="10" t="n"/>
+      <c r="D324" s="10" t="n"/>
+      <c r="E324" s="10" t="n"/>
+    </row>
     <row r="325" ht="15.75" customHeight="1" s="11">
-      <c r="A325" s="13" t="inlineStr">
+      <c r="A325" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B325" s="10" t="n"/>
+      <c r="C325" s="10" t="n"/>
+      <c r="D325" s="10" t="n"/>
+      <c r="E325" s="10" t="n"/>
+    </row>
+    <row r="326" ht="15.75" customHeight="1" s="11"/>
+    <row r="327" ht="15.75" customHeight="1" s="11">
+      <c r="A327" s="13" t="inlineStr">
         <is>
           <t>Декабрь 2026</t>
         </is>
       </c>
     </row>
-    <row r="326" ht="15.75" customHeight="1" s="11">
-      <c r="A326" s="5" t="inlineStr">
+    <row r="328" ht="15.75" customHeight="1" s="11">
+      <c r="A328" s="5" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B326" s="6" t="inlineStr">
+      <c r="B328" s="6" t="inlineStr">
         <is>
           <t>Большой пр. В.О</t>
         </is>
       </c>
-      <c r="C326" s="6" t="inlineStr">
+      <c r="C328" s="6" t="inlineStr">
         <is>
           <t>Лиговский</t>
         </is>
       </c>
-      <c r="D326" s="6" t="inlineStr">
+      <c r="D328" s="6" t="inlineStr">
         <is>
           <t>Кременчугская</t>
         </is>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="E328" s="6" t="inlineStr">
         <is>
           <t>Варшавская</t>
         </is>
       </c>
-      <c r="F326" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <t>Общая</t>
         </is>
       </c>
-    </row>
-    <row r="327" ht="15.75" customHeight="1" s="11">
-      <c r="A327" s="7" t="inlineStr">
-        <is>
-          <t>Выручка</t>
-        </is>
-      </c>
-      <c r="B327" s="10" t="n"/>
-      <c r="C327" s="10" t="n"/>
-      <c r="D327" s="10" t="n"/>
-      <c r="E327" s="10" t="n"/>
-    </row>
-    <row r="328" ht="15.75" customHeight="1" s="11">
-      <c r="A328" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль</t>
-        </is>
-      </c>
-      <c r="B328" s="10" t="n"/>
-      <c r="C328" s="10" t="n"/>
-      <c r="D328" s="10" t="n"/>
-      <c r="E328" s="10" t="n"/>
     </row>
     <row r="329" ht="15.75" customHeight="1" s="11">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>Чеки</t>
+          <t>Выручка</t>
         </is>
       </c>
       <c r="B329" s="10" t="n"/>
@@ -4394,7 +4418,7 @@
     <row r="330" ht="15.75" customHeight="1" s="11">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>Средний чек</t>
+          <t>Прибыль</t>
         </is>
       </c>
       <c r="B330" s="10" t="n"/>
@@ -4405,7 +4429,7 @@
     <row r="331" ht="15.75" customHeight="1" s="11">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>Доля розлив</t>
+          <t>Чеки</t>
         </is>
       </c>
       <c r="B331" s="10" t="n"/>
@@ -4416,7 +4440,7 @@
     <row r="332" ht="15.75" customHeight="1" s="11">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>Доля фасовка</t>
+          <t>Средний чек</t>
         </is>
       </c>
       <c r="B332" s="10" t="n"/>
@@ -4427,7 +4451,7 @@
     <row r="333" ht="15.75" customHeight="1" s="11">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>Доля кухня</t>
+          <t>Доля розлив</t>
         </is>
       </c>
       <c r="B333" s="10" t="n"/>
@@ -4438,7 +4462,7 @@
     <row r="334" ht="15.75" customHeight="1" s="11">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Доля фасовка</t>
         </is>
       </c>
       <c r="B334" s="10" t="n"/>
@@ -4449,7 +4473,7 @@
     <row r="335" ht="15.75" customHeight="1" s="11">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>Наценка розлив</t>
+          <t>Доля кухня</t>
         </is>
       </c>
       <c r="B335" s="10" t="n"/>
@@ -4460,7 +4484,7 @@
     <row r="336" ht="15.75" customHeight="1" s="11">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>Наценка фасовка</t>
+          <t>Наценка</t>
         </is>
       </c>
       <c r="B336" s="10" t="n"/>
@@ -4471,7 +4495,7 @@
     <row r="337" ht="15.75" customHeight="1" s="11">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>Наценка кухня</t>
+          <t>Наценка розлив</t>
         </is>
       </c>
       <c r="B337" s="10" t="n"/>
@@ -4479,8 +4503,28 @@
       <c r="D337" s="10" t="n"/>
       <c r="E337" s="10" t="n"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1" s="11"/>
-    <row r="339" ht="15.75" customHeight="1" s="11"/>
+    <row r="338" ht="15.75" customHeight="1" s="11">
+      <c r="A338" s="7" t="inlineStr">
+        <is>
+          <t>Наценка фасовка</t>
+        </is>
+      </c>
+      <c r="B338" s="10" t="n"/>
+      <c r="C338" s="10" t="n"/>
+      <c r="D338" s="10" t="n"/>
+      <c r="E338" s="10" t="n"/>
+    </row>
+    <row r="339" ht="15.75" customHeight="1" s="11">
+      <c r="A339" s="7" t="inlineStr">
+        <is>
+          <t>Наценка кухня</t>
+        </is>
+      </c>
+      <c r="B339" s="10" t="n"/>
+      <c r="C339" s="10" t="n"/>
+      <c r="D339" s="10" t="n"/>
+      <c r="E339" s="10" t="n"/>
+    </row>
     <row r="340" ht="15.75" customHeight="1" s="11"/>
     <row r="341" ht="15.75" customHeight="1" s="11"/>
     <row r="342" ht="15.75" customHeight="1" s="11"/>

--- a/планы_2025_2026.xlsx
+++ b/планы_2025_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wwwor\OneDrive\Документы\GitHub\beer-abc-analysis\data\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Documents\GitHub\beer-abc-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A85E419-A267-4350-81A5-6A15FCE46732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F56D3D-C577-42A0-ADFB-26EAAD563257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Планы 2025-2026" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="46">
   <si>
     <t>ПЛАНЫ НА 2025-2026 ГОД</t>
   </si>
@@ -424,24 +424,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -463,6 +445,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -680,20 +680,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1003"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -718,7 +718,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -746,12 +746,12 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:26" ht="18" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -776,7 +776,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -816,7 +816,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -846,7 +846,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -876,7 +876,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -906,7 +906,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
@@ -936,7 +936,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
@@ -966,7 +966,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
@@ -996,7 +996,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>14</v>
       </c>
@@ -1026,7 +1026,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
@@ -1056,7 +1056,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
@@ -1086,7 +1086,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
@@ -1116,7 +1116,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
@@ -1146,7 +1146,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1174,12 +1174,12 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="17" spans="1:26" ht="18" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1204,7 +1204,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>2</v>
       </c>
@@ -1244,7 +1244,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>8</v>
       </c>
@@ -1274,7 +1274,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>9</v>
       </c>
@@ -1304,7 +1304,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>10</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>11</v>
       </c>
@@ -1364,7 +1364,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>12</v>
       </c>
@@ -1394,7 +1394,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>13</v>
       </c>
@@ -1424,7 +1424,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>14</v>
       </c>
@@ -1454,7 +1454,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
@@ -1484,7 +1484,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>16</v>
       </c>
@@ -1514,7 +1514,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
@@ -1544,7 +1544,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -1574,7 +1574,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1602,12 +1602,12 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -1632,7 +1632,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>2</v>
       </c>
@@ -1672,7 +1672,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>8</v>
       </c>
@@ -1702,7 +1702,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>9</v>
       </c>
@@ -1732,7 +1732,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>10</v>
       </c>
@@ -1762,7 +1762,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>11</v>
       </c>
@@ -1792,7 +1792,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>12</v>
       </c>
@@ -1822,7 +1822,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>13</v>
       </c>
@@ -1852,7 +1852,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>14</v>
       </c>
@@ -1882,7 +1882,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>15</v>
       </c>
@@ -1912,7 +1912,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>16</v>
       </c>
@@ -1942,7 +1942,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>17</v>
       </c>
@@ -1972,7 +1972,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>18</v>
       </c>
@@ -2002,7 +2002,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2030,12 +2030,12 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
+    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -2060,7 +2060,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>2</v>
       </c>
@@ -2100,7 +2100,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>8</v>
       </c>
@@ -2130,7 +2130,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>9</v>
       </c>
@@ -2160,7 +2160,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>10</v>
       </c>
@@ -2190,7 +2190,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>11</v>
       </c>
@@ -2220,7 +2220,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>12</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>13</v>
       </c>
@@ -2280,7 +2280,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>14</v>
       </c>
@@ -2310,7 +2310,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>15</v>
       </c>
@@ -2340,7 +2340,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>16</v>
       </c>
@@ -2370,7 +2370,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>17</v>
       </c>
@@ -2400,7 +2400,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>18</v>
       </c>
@@ -2430,7 +2430,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2458,12 +2458,12 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="17" t="s">
+    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -2488,7 +2488,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>2</v>
       </c>
@@ -2528,7 +2528,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>8</v>
       </c>
@@ -2558,7 +2558,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>9</v>
       </c>
@@ -2588,7 +2588,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>10</v>
       </c>
@@ -2618,7 +2618,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>11</v>
       </c>
@@ -2648,7 +2648,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>12</v>
       </c>
@@ -2678,7 +2678,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>13</v>
       </c>
@@ -2708,7 +2708,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>14</v>
       </c>
@@ -2738,7 +2738,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>15</v>
       </c>
@@ -2768,7 +2768,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>16</v>
       </c>
@@ -2798,7 +2798,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>17</v>
       </c>
@@ -2828,7 +2828,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>18</v>
       </c>
@@ -2858,7 +2858,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2886,12 +2886,12 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="17" t="s">
+    <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B73" s="16"/>
-      <c r="C73" s="16"/>
+      <c r="B73" s="24"/>
+      <c r="C73" s="24"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -2916,7 +2916,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>2</v>
       </c>
@@ -2956,7 +2956,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>8</v>
       </c>
@@ -2986,7 +2986,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>9</v>
       </c>
@@ -3016,7 +3016,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>10</v>
       </c>
@@ -3046,7 +3046,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>11</v>
       </c>
@@ -3076,7 +3076,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>12</v>
       </c>
@@ -3106,7 +3106,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>13</v>
       </c>
@@ -3136,7 +3136,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>14</v>
       </c>
@@ -3166,7 +3166,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>15</v>
       </c>
@@ -3196,7 +3196,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>16</v>
       </c>
@@ -3226,7 +3226,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>17</v>
       </c>
@@ -3256,7 +3256,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>18</v>
       </c>
@@ -3286,7 +3286,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3314,12 +3314,12 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="17" t="s">
+    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16"/>
+      <c r="B87" s="24"/>
+      <c r="C87" s="24"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
@@ -3344,7 +3344,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>2</v>
       </c>
@@ -3384,7 +3384,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>8</v>
       </c>
@@ -3414,7 +3414,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>9</v>
       </c>
@@ -3444,7 +3444,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>10</v>
       </c>
@@ -3474,7 +3474,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>11</v>
       </c>
@@ -3504,7 +3504,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>12</v>
       </c>
@@ -3534,7 +3534,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>13</v>
       </c>
@@ -3564,7 +3564,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>14</v>
       </c>
@@ -3594,7 +3594,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>15</v>
       </c>
@@ -3624,7 +3624,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>16</v>
       </c>
@@ -3654,7 +3654,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>17</v>
       </c>
@@ -3684,7 +3684,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>18</v>
       </c>
@@ -3714,7 +3714,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3742,12 +3742,12 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="17" t="s">
+    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B101" s="16"/>
-      <c r="C101" s="16"/>
+      <c r="B101" s="24"/>
+      <c r="C101" s="24"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
@@ -3772,7 +3772,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>2</v>
       </c>
@@ -3812,7 +3812,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>8</v>
       </c>
@@ -3842,7 +3842,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>9</v>
       </c>
@@ -3872,7 +3872,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>10</v>
       </c>
@@ -3902,7 +3902,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>11</v>
       </c>
@@ -3932,7 +3932,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>12</v>
       </c>
@@ -3962,7 +3962,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>13</v>
       </c>
@@ -3992,7 +3992,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>14</v>
       </c>
@@ -4022,7 +4022,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>15</v>
       </c>
@@ -4052,7 +4052,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>16</v>
       </c>
@@ -4082,7 +4082,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>17</v>
       </c>
@@ -4112,7 +4112,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>18</v>
       </c>
@@ -4142,7 +4142,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4170,12 +4170,12 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="17" t="s">
+    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B115" s="16"/>
-      <c r="C115" s="16"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
@@ -4200,7 +4200,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>2</v>
       </c>
@@ -4240,7 +4240,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>8</v>
       </c>
@@ -4279,7 +4279,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>27</v>
       </c>
@@ -4324,7 +4324,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>9</v>
       </c>
@@ -4364,7 +4364,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>10</v>
       </c>
@@ -4403,7 +4403,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>11</v>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
         <v>12</v>
       </c>
@@ -4481,7 +4481,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
         <v>13</v>
       </c>
@@ -4520,7 +4520,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
         <v>14</v>
       </c>
@@ -4559,7 +4559,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="11" t="s">
         <v>15</v>
       </c>
@@ -4598,7 +4598,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="11" t="s">
         <v>16</v>
       </c>
@@ -4637,7 +4637,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="11" t="s">
         <v>17</v>
       </c>
@@ -4676,7 +4676,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="11" t="s">
         <v>18</v>
       </c>
@@ -4715,7 +4715,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="10"/>
       <c r="B129" s="10"/>
       <c r="C129" s="10"/>
@@ -4743,12 +4743,12 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="21" t="s">
+    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B130" s="19"/>
-      <c r="C130" s="20"/>
+      <c r="B130" s="26"/>
+      <c r="C130" s="27"/>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
@@ -4773,7 +4773,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>2</v>
       </c>
@@ -4813,7 +4813,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="11" t="s">
         <v>8</v>
       </c>
@@ -4854,7 +4854,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>27</v>
       </c>
@@ -4899,7 +4899,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="11" t="s">
         <v>9</v>
       </c>
@@ -4940,7 +4940,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="11" t="s">
         <v>10</v>
       </c>
@@ -4981,7 +4981,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="11" t="s">
         <v>11</v>
       </c>
@@ -5022,7 +5022,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="11" t="s">
         <v>12</v>
       </c>
@@ -5063,7 +5063,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="11" t="s">
         <v>13</v>
       </c>
@@ -5104,7 +5104,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="11" t="s">
         <v>14</v>
       </c>
@@ -5145,7 +5145,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="11" t="s">
         <v>15</v>
       </c>
@@ -5186,7 +5186,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="11" t="s">
         <v>16</v>
       </c>
@@ -5227,7 +5227,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
         <v>17</v>
       </c>
@@ -5268,7 +5268,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
         <v>18</v>
       </c>
@@ -5309,10 +5309,10 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="22"/>
-      <c r="B144" s="19"/>
-      <c r="C144" s="20"/>
+    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="29"/>
+      <c r="B144" s="26"/>
+      <c r="C144" s="27"/>
       <c r="D144" s="8"/>
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
@@ -5337,7 +5337,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="13" t="s">
         <v>29</v>
       </c>
@@ -5367,7 +5367,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>2</v>
       </c>
@@ -5407,7 +5407,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="11" t="s">
         <v>8</v>
       </c>
@@ -5448,7 +5448,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
         <v>27</v>
       </c>
@@ -5493,7 +5493,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="11" t="s">
         <v>9</v>
       </c>
@@ -5534,7 +5534,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="11" t="s">
         <v>10</v>
       </c>
@@ -5575,7 +5575,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="11" t="s">
         <v>11</v>
       </c>
@@ -5616,7 +5616,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="11" t="s">
         <v>12</v>
       </c>
@@ -5657,7 +5657,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="11" t="s">
         <v>13</v>
       </c>
@@ -5698,7 +5698,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="11" t="s">
         <v>14</v>
       </c>
@@ -5739,7 +5739,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="11" t="s">
         <v>15</v>
       </c>
@@ -5780,7 +5780,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="11" t="s">
         <v>16</v>
       </c>
@@ -5821,7 +5821,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="11" t="s">
         <v>17</v>
       </c>
@@ -5862,7 +5862,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="11" t="s">
         <v>18</v>
       </c>
@@ -5903,7 +5903,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -5931,7 +5931,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="13" t="s">
         <v>30</v>
       </c>
@@ -5960,7 +5960,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>2</v>
       </c>
@@ -6000,7 +6000,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="11" t="s">
         <v>8</v>
       </c>
@@ -6041,7 +6041,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>27</v>
       </c>
@@ -6086,7 +6086,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="11" t="s">
         <v>9</v>
       </c>
@@ -6127,7 +6127,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="11" t="s">
         <v>10</v>
       </c>
@@ -6168,7 +6168,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="11" t="s">
         <v>11</v>
       </c>
@@ -6209,7 +6209,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="11" t="s">
         <v>12</v>
       </c>
@@ -6250,7 +6250,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="11" t="s">
         <v>13</v>
       </c>
@@ -6291,7 +6291,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="11" t="s">
         <v>14</v>
       </c>
@@ -6332,7 +6332,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
     </row>
-    <row r="170" spans="1:26" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:26" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="11" t="s">
         <v>15</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>194.48499999999999</v>
       </c>
       <c r="G170" s="1"/>
-      <c r="H170" s="27">
+      <c r="H170" s="19">
         <v>260</v>
       </c>
       <c r="I170" s="1"/>
@@ -6375,7 +6375,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
     </row>
-    <row r="171" spans="1:26" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:26" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="11" t="s">
         <v>16</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>250</v>
       </c>
       <c r="G171" s="1"/>
-      <c r="H171" s="28">
+      <c r="H171" s="20">
         <v>120</v>
       </c>
       <c r="I171" s="1"/>
@@ -6418,7 +6418,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
     </row>
-    <row r="172" spans="1:26" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:26" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="11" t="s">
         <v>17</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>122.5</v>
       </c>
       <c r="G172" s="1"/>
-      <c r="H172" s="29">
+      <c r="H172" s="21">
         <v>170</v>
       </c>
       <c r="I172" s="1"/>
@@ -6461,7 +6461,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
     </row>
-    <row r="173" spans="1:26" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:26" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A173" s="11" t="s">
         <v>18</v>
       </c>
@@ -6502,7 +6502,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
     </row>
-    <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6530,7 +6530,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="14" t="s">
         <v>31</v>
       </c>
@@ -6560,7 +6560,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
     </row>
-    <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>2</v>
       </c>
@@ -6600,29 +6600,29 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
     </row>
-    <row r="177" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="30" t="s">
+    <row r="177" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B177" s="30">
+      <c r="B177" s="22">
         <v>910800</v>
       </c>
-      <c r="C177" s="30">
+      <c r="C177" s="22">
         <v>910800</v>
       </c>
-      <c r="D177" s="30">
+      <c r="D177" s="22">
         <v>1302400</v>
       </c>
-      <c r="E177" s="30">
+      <c r="E177" s="22">
         <v>910800</v>
       </c>
-      <c r="F177" s="30">
+      <c r="F177" s="22">
         <f t="shared" ref="F177" si="12">SUM(B177:E177)</f>
         <v>4034800</v>
       </c>
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
-      <c r="I177" s="26" t="s">
+      <c r="I177" s="18" t="s">
         <v>44</v>
       </c>
       <c r="J177" s="1"/>
@@ -6643,27 +6643,27 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="30" t="s">
+    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B178" s="30">
+      <c r="B178" s="22">
         <f t="shared" ref="B178:E178" si="13">B177*0.05</f>
         <v>45540</v>
       </c>
-      <c r="C178" s="30">
+      <c r="C178" s="22">
         <f t="shared" si="13"/>
         <v>45540</v>
       </c>
-      <c r="D178" s="30">
+      <c r="D178" s="22">
         <f t="shared" si="13"/>
         <v>65120</v>
       </c>
-      <c r="E178" s="30">
+      <c r="E178" s="22">
         <f t="shared" si="13"/>
         <v>45540</v>
       </c>
-      <c r="F178" s="30">
+      <c r="F178" s="22">
         <f t="shared" ref="F178:F180" si="14">SUM(B178:E178)</f>
         <v>201740</v>
       </c>
@@ -6688,23 +6688,23 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="30" t="s">
+    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B179" s="30">
+      <c r="B179" s="22">
         <v>602953.85</v>
       </c>
-      <c r="C179" s="30">
+      <c r="C179" s="22">
         <v>582223.27</v>
       </c>
-      <c r="D179" s="30">
+      <c r="D179" s="22">
         <v>864977.78</v>
       </c>
-      <c r="E179" s="30">
+      <c r="E179" s="22">
         <v>612584.13</v>
       </c>
-      <c r="F179" s="30">
+      <c r="F179" s="22">
         <f t="shared" si="14"/>
         <v>2662739.0300000003</v>
       </c>
@@ -6729,23 +6729,23 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="30" t="s">
+    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B180" s="30">
+      <c r="B180" s="22">
         <v>660</v>
       </c>
-      <c r="C180" s="30">
+      <c r="C180" s="22">
         <v>660</v>
       </c>
-      <c r="D180" s="30">
+      <c r="D180" s="22">
         <v>740</v>
       </c>
-      <c r="E180" s="30">
+      <c r="E180" s="22">
         <v>660</v>
       </c>
-      <c r="F180" s="30">
+      <c r="F180" s="22">
         <f t="shared" si="14"/>
         <v>2720</v>
       </c>
@@ -6770,23 +6770,23 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
     </row>
-    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="30" t="s">
+    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B181" s="30">
+      <c r="B181" s="22">
         <v>1380</v>
       </c>
-      <c r="C181" s="30" t="s">
+      <c r="C181" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D181" s="30" t="s">
+      <c r="D181" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E181" s="30" t="s">
+      <c r="E181" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="F181" s="30">
+      <c r="F181" s="22">
         <f t="shared" ref="F181:F188" si="15">AVERAGE(B181:E181)</f>
         <v>1380</v>
       </c>
@@ -6811,23 +6811,23 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
     </row>
-    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="30" t="s">
+    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B182" s="30">
+      <c r="B182" s="22">
         <v>60</v>
       </c>
-      <c r="C182" s="30">
+      <c r="C182" s="22">
         <v>60</v>
       </c>
-      <c r="D182" s="30">
+      <c r="D182" s="22">
         <v>60</v>
       </c>
-      <c r="E182" s="30">
+      <c r="E182" s="22">
         <v>60</v>
       </c>
-      <c r="F182" s="30">
+      <c r="F182" s="22">
         <f t="shared" si="15"/>
         <v>60</v>
       </c>
@@ -6852,23 +6852,23 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
     </row>
-    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="30" t="s">
+    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B183" s="30">
+      <c r="B183" s="22">
         <v>25</v>
       </c>
-      <c r="C183" s="30">
+      <c r="C183" s="22">
         <v>25</v>
       </c>
-      <c r="D183" s="30">
+      <c r="D183" s="22">
         <v>25</v>
       </c>
-      <c r="E183" s="30">
+      <c r="E183" s="22">
         <v>23</v>
       </c>
-      <c r="F183" s="30">
+      <c r="F183" s="22">
         <f t="shared" si="15"/>
         <v>24.5</v>
       </c>
@@ -6893,23 +6893,23 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
     </row>
-    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="30" t="s">
+    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B184" s="30">
+      <c r="B184" s="22">
         <v>15</v>
       </c>
-      <c r="C184" s="30">
+      <c r="C184" s="22">
         <v>15</v>
       </c>
-      <c r="D184" s="30">
+      <c r="D184" s="22">
         <v>15</v>
       </c>
-      <c r="E184" s="30">
+      <c r="E184" s="22">
         <v>17</v>
       </c>
-      <c r="F184" s="30">
+      <c r="F184" s="22">
         <f t="shared" si="15"/>
         <v>15.5</v>
       </c>
@@ -6934,23 +6934,23 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
     </row>
-    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="30" t="s">
+    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B185" s="30">
+      <c r="B185" s="22">
         <v>195.86</v>
       </c>
-      <c r="C185" s="30">
+      <c r="C185" s="22">
         <v>177.2</v>
       </c>
-      <c r="D185" s="30">
+      <c r="D185" s="22">
         <v>197.74</v>
       </c>
-      <c r="E185" s="30">
+      <c r="E185" s="22">
         <v>205.42</v>
       </c>
-      <c r="F185" s="30">
+      <c r="F185" s="22">
         <f t="shared" si="15"/>
         <v>194.05499999999998</v>
       </c>
@@ -6975,23 +6975,23 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="30" t="s">
+    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B186" s="30">
+      <c r="B186" s="22">
         <v>260</v>
       </c>
-      <c r="C186" s="30">
+      <c r="C186" s="22">
         <v>210</v>
       </c>
-      <c r="D186" s="30">
+      <c r="D186" s="22">
         <v>260</v>
       </c>
-      <c r="E186" s="30">
+      <c r="E186" s="22">
         <v>270</v>
       </c>
-      <c r="F186" s="30">
+      <c r="F186" s="22">
         <f t="shared" si="15"/>
         <v>250</v>
       </c>
@@ -7016,23 +7016,23 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="30" t="s">
+    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B187" s="30">
+      <c r="B187" s="22">
         <v>120</v>
       </c>
-      <c r="C187" s="30">
+      <c r="C187" s="22">
         <v>120</v>
       </c>
-      <c r="D187" s="30">
+      <c r="D187" s="22">
         <v>120</v>
       </c>
-      <c r="E187" s="30">
+      <c r="E187" s="22">
         <v>120</v>
       </c>
-      <c r="F187" s="30">
+      <c r="F187" s="22">
         <f t="shared" si="15"/>
         <v>120</v>
       </c>
@@ -7057,23 +7057,23 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="30" t="s">
+    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B188" s="30">
+      <c r="B188" s="22">
         <v>160</v>
       </c>
-      <c r="C188" s="30">
+      <c r="C188" s="22">
         <v>180</v>
       </c>
-      <c r="D188" s="30">
+      <c r="D188" s="22">
         <v>170</v>
       </c>
-      <c r="E188" s="30">
+      <c r="E188" s="22">
         <v>180</v>
       </c>
-      <c r="F188" s="30">
+      <c r="F188" s="22">
         <f t="shared" si="15"/>
         <v>172.5</v>
       </c>
@@ -7098,13 +7098,13 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
     </row>
-    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="23"/>
-      <c r="B189" s="24"/>
-      <c r="C189" s="24"/>
-      <c r="D189" s="24"/>
-      <c r="E189" s="24"/>
-      <c r="F189" s="25"/>
+    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="15"/>
+      <c r="B189" s="16"/>
+      <c r="C189" s="16"/>
+      <c r="D189" s="16"/>
+      <c r="E189" s="16"/>
+      <c r="F189" s="17"/>
       <c r="G189" s="1"/>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
@@ -7126,7 +7126,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="14" t="s">
         <v>32</v>
       </c>
@@ -7156,7 +7156,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>2</v>
       </c>
@@ -7196,15 +7196,26 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="4" t="s">
+    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B192" s="5"/>
-      <c r="C192" s="5"/>
-      <c r="D192" s="5"/>
-      <c r="E192" s="5"/>
-      <c r="F192" s="1"/>
+      <c r="B192">
+        <v>889952</v>
+      </c>
+      <c r="C192">
+        <v>889952</v>
+      </c>
+      <c r="D192">
+        <v>1249812</v>
+      </c>
+      <c r="E192">
+        <v>869968</v>
+      </c>
+      <c r="F192" s="22">
+        <f t="shared" ref="F192" si="16">SUM(B192:E192)</f>
+        <v>3899684</v>
+      </c>
       <c r="G192" s="1"/>
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
@@ -7226,15 +7237,30 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B193" s="5"/>
-      <c r="C193" s="5"/>
-      <c r="D193" s="5"/>
-      <c r="E193" s="5"/>
-      <c r="F193" s="1"/>
+    <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B193" s="22">
+        <f t="shared" ref="B193:E193" si="17">B192*0.05</f>
+        <v>44497.600000000006</v>
+      </c>
+      <c r="C193" s="22">
+        <f t="shared" si="17"/>
+        <v>44497.600000000006</v>
+      </c>
+      <c r="D193" s="22">
+        <f t="shared" si="17"/>
+        <v>62490.600000000006</v>
+      </c>
+      <c r="E193" s="22">
+        <f t="shared" si="17"/>
+        <v>43498.400000000001</v>
+      </c>
+      <c r="F193" s="22">
+        <f t="shared" ref="F193:F195" si="18">SUM(B193:E193)</f>
+        <v>194984.2</v>
+      </c>
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
@@ -7256,15 +7282,30 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B194" s="5"/>
-      <c r="C194" s="5"/>
-      <c r="D194" s="5"/>
-      <c r="E194" s="5"/>
-      <c r="F194" s="1"/>
+    <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B194" s="22">
+        <f>B192*(1 - 1 / (1 + B200 / 100))</f>
+        <v>595421.94969552557</v>
+      </c>
+      <c r="C194" s="22">
+        <f t="shared" ref="C194:E194" si="19">C192*(1 - 1 / (1 + C200 / 100))</f>
+        <v>595421.94969552557</v>
+      </c>
+      <c r="D194" s="22">
+        <f t="shared" si="19"/>
+        <v>836186.10643367749</v>
+      </c>
+      <c r="E194" s="22">
+        <f t="shared" si="19"/>
+        <v>582051.66428382311</v>
+      </c>
+      <c r="F194" s="22">
+        <f t="shared" si="18"/>
+        <v>2609081.6701085516</v>
+      </c>
       <c r="G194" s="1"/>
       <c r="H194" s="1"/>
       <c r="I194" s="1"/>
@@ -7286,15 +7327,30 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B195" s="5"/>
-      <c r="C195" s="5"/>
-      <c r="D195" s="5"/>
-      <c r="E195" s="5"/>
-      <c r="F195" s="1"/>
+    <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B195" s="22">
+        <f>B192/B196</f>
+        <v>585.49473684210523</v>
+      </c>
+      <c r="C195" s="22">
+        <f t="shared" ref="C195:E195" si="20">C192/C196</f>
+        <v>585.49473684210523</v>
+      </c>
+      <c r="D195" s="22">
+        <f t="shared" si="20"/>
+        <v>739.53372781065093</v>
+      </c>
+      <c r="E195" s="22">
+        <f t="shared" si="20"/>
+        <v>572.34736842105258</v>
+      </c>
+      <c r="F195" s="22">
+        <f t="shared" si="18"/>
+        <v>2482.8705699159141</v>
+      </c>
       <c r="G195" s="1"/>
       <c r="H195" s="1"/>
       <c r="I195" s="1"/>
@@ -7316,15 +7372,26 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B196" s="5"/>
-      <c r="C196" s="5"/>
-      <c r="D196" s="5"/>
-      <c r="E196" s="5"/>
-      <c r="F196" s="1"/>
+    <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B196" s="22">
+        <v>1520</v>
+      </c>
+      <c r="C196" s="22">
+        <v>1520</v>
+      </c>
+      <c r="D196" s="22">
+        <v>1690</v>
+      </c>
+      <c r="E196" s="22">
+        <v>1520</v>
+      </c>
+      <c r="F196" s="22">
+        <f t="shared" ref="F196:F203" si="21">AVERAGE(B196:E196)</f>
+        <v>1562.5</v>
+      </c>
       <c r="G196" s="1"/>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
@@ -7346,15 +7413,26 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B197" s="5"/>
-      <c r="C197" s="5"/>
-      <c r="D197" s="5"/>
-      <c r="E197" s="5"/>
-      <c r="F197" s="1"/>
+    <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B197" s="22">
+        <v>60</v>
+      </c>
+      <c r="C197" s="22">
+        <v>60</v>
+      </c>
+      <c r="D197" s="22">
+        <v>60</v>
+      </c>
+      <c r="E197" s="22">
+        <v>60</v>
+      </c>
+      <c r="F197" s="22">
+        <f t="shared" si="21"/>
+        <v>60</v>
+      </c>
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
       <c r="I197" s="1"/>
@@ -7376,15 +7454,26 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B198" s="5"/>
-      <c r="C198" s="5"/>
-      <c r="D198" s="5"/>
-      <c r="E198" s="5"/>
-      <c r="F198" s="1"/>
+    <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B198" s="22">
+        <v>22</v>
+      </c>
+      <c r="C198" s="22">
+        <v>22</v>
+      </c>
+      <c r="D198" s="22">
+        <v>22</v>
+      </c>
+      <c r="E198" s="22">
+        <v>22</v>
+      </c>
+      <c r="F198" s="22">
+        <f t="shared" si="21"/>
+        <v>22</v>
+      </c>
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
       <c r="I198" s="1"/>
@@ -7406,15 +7495,26 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" s="5"/>
-      <c r="C199" s="5"/>
-      <c r="D199" s="5"/>
-      <c r="E199" s="5"/>
-      <c r="F199" s="1"/>
+    <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" s="22">
+        <v>18</v>
+      </c>
+      <c r="C199" s="22">
+        <v>18</v>
+      </c>
+      <c r="D199" s="22">
+        <v>18</v>
+      </c>
+      <c r="E199" s="22">
+        <v>18</v>
+      </c>
+      <c r="F199" s="22">
+        <f t="shared" si="21"/>
+        <v>18</v>
+      </c>
       <c r="G199" s="1"/>
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
@@ -7436,15 +7536,26 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B200" s="5"/>
-      <c r="C200" s="5"/>
-      <c r="D200" s="5"/>
-      <c r="E200" s="5"/>
-      <c r="F200" s="1"/>
+    <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200">
+        <v>202.16</v>
+      </c>
+      <c r="C200">
+        <v>202.16</v>
+      </c>
+      <c r="D200">
+        <v>202.16</v>
+      </c>
+      <c r="E200">
+        <v>202.16</v>
+      </c>
+      <c r="F200" s="22">
+        <f t="shared" si="21"/>
+        <v>202.16</v>
+      </c>
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
       <c r="I200" s="1"/>
@@ -7466,15 +7577,26 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B201" s="5"/>
-      <c r="C201" s="5"/>
-      <c r="D201" s="5"/>
-      <c r="E201" s="5"/>
-      <c r="F201" s="1"/>
+    <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B201" s="22">
+        <v>260</v>
+      </c>
+      <c r="C201" s="22">
+        <v>260</v>
+      </c>
+      <c r="D201" s="22">
+        <v>260</v>
+      </c>
+      <c r="E201" s="22">
+        <v>260</v>
+      </c>
+      <c r="F201" s="22">
+        <f t="shared" si="21"/>
+        <v>260</v>
+      </c>
       <c r="G201" s="1"/>
       <c r="H201" s="1"/>
       <c r="I201" s="1"/>
@@ -7496,15 +7618,26 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B202" s="5"/>
-      <c r="C202" s="5"/>
-      <c r="D202" s="5"/>
-      <c r="E202" s="5"/>
-      <c r="F202" s="1"/>
+    <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B202" s="22">
+        <v>120</v>
+      </c>
+      <c r="C202" s="22">
+        <v>120</v>
+      </c>
+      <c r="D202" s="22">
+        <v>120</v>
+      </c>
+      <c r="E202" s="22">
+        <v>120</v>
+      </c>
+      <c r="F202" s="22">
+        <f t="shared" si="21"/>
+        <v>120</v>
+      </c>
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
       <c r="I202" s="1"/>
@@ -7526,13 +7659,26 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="1"/>
-      <c r="B203" s="1"/>
-      <c r="C203" s="1"/>
-      <c r="D203" s="1"/>
-      <c r="E203" s="1"/>
-      <c r="F203" s="1"/>
+    <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B203" s="22">
+        <v>180</v>
+      </c>
+      <c r="C203" s="22">
+        <v>180</v>
+      </c>
+      <c r="D203" s="22">
+        <v>180</v>
+      </c>
+      <c r="E203" s="22">
+        <v>180</v>
+      </c>
+      <c r="F203" s="22">
+        <f t="shared" si="21"/>
+        <v>180</v>
+      </c>
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
       <c r="I203" s="1"/>
@@ -7554,7 +7700,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="14" t="s">
         <v>33</v>
       </c>
@@ -7584,7 +7730,7 @@
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
     </row>
-    <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>2</v>
       </c>
@@ -7624,7 +7770,7 @@
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
     </row>
-    <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>8</v>
       </c>
@@ -7654,7 +7800,7 @@
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
     </row>
-    <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>9</v>
       </c>
@@ -7684,7 +7830,7 @@
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
     </row>
-    <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>10</v>
       </c>
@@ -7714,7 +7860,7 @@
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
     </row>
-    <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>11</v>
       </c>
@@ -7744,7 +7890,7 @@
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
     </row>
-    <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>12</v>
       </c>
@@ -7774,7 +7920,7 @@
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
     </row>
-    <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>13</v>
       </c>
@@ -7804,7 +7950,7 @@
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
     </row>
-    <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>14</v>
       </c>
@@ -7834,7 +7980,7 @@
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
     </row>
-    <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>15</v>
       </c>
@@ -7864,7 +8010,7 @@
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
     </row>
-    <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>16</v>
       </c>
@@ -7894,7 +8040,7 @@
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
     </row>
-    <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>17</v>
       </c>
@@ -7924,7 +8070,7 @@
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
     </row>
-    <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>18</v>
       </c>
@@ -7954,7 +8100,7 @@
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
     </row>
-    <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7982,7 +8128,7 @@
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
     </row>
-    <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="14" t="s">
         <v>34</v>
       </c>
@@ -8012,7 +8158,7 @@
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
     </row>
-    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>2</v>
       </c>
@@ -8052,7 +8198,7 @@
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
     </row>
-    <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>8</v>
       </c>
@@ -8082,7 +8228,7 @@
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
     </row>
-    <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>9</v>
       </c>
@@ -8112,7 +8258,7 @@
       <c r="Y221" s="1"/>
       <c r="Z221" s="1"/>
     </row>
-    <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>10</v>
       </c>
@@ -8142,7 +8288,7 @@
       <c r="Y222" s="1"/>
       <c r="Z222" s="1"/>
     </row>
-    <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>11</v>
       </c>
@@ -8172,7 +8318,7 @@
       <c r="Y223" s="1"/>
       <c r="Z223" s="1"/>
     </row>
-    <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>12</v>
       </c>
@@ -8202,7 +8348,7 @@
       <c r="Y224" s="1"/>
       <c r="Z224" s="1"/>
     </row>
-    <row r="225" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>13</v>
       </c>
@@ -8232,7 +8378,7 @@
       <c r="Y225" s="1"/>
       <c r="Z225" s="1"/>
     </row>
-    <row r="226" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>14</v>
       </c>
@@ -8262,7 +8408,7 @@
       <c r="Y226" s="1"/>
       <c r="Z226" s="1"/>
     </row>
-    <row r="227" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>15</v>
       </c>
@@ -8292,7 +8438,7 @@
       <c r="Y227" s="1"/>
       <c r="Z227" s="1"/>
     </row>
-    <row r="228" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>16</v>
       </c>
@@ -8322,7 +8468,7 @@
       <c r="Y228" s="1"/>
       <c r="Z228" s="1"/>
     </row>
-    <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>17</v>
       </c>
@@ -8352,7 +8498,7 @@
       <c r="Y229" s="1"/>
       <c r="Z229" s="1"/>
     </row>
-    <row r="230" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>18</v>
       </c>
@@ -8382,7 +8528,7 @@
       <c r="Y230" s="1"/>
       <c r="Z230" s="1"/>
     </row>
-    <row r="231" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -8410,7 +8556,7 @@
       <c r="Y231" s="1"/>
       <c r="Z231" s="1"/>
     </row>
-    <row r="232" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="14" t="s">
         <v>35</v>
       </c>
@@ -8440,7 +8586,7 @@
       <c r="Y232" s="1"/>
       <c r="Z232" s="1"/>
     </row>
-    <row r="233" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>2</v>
       </c>
@@ -8480,7 +8626,7 @@
       <c r="Y233" s="1"/>
       <c r="Z233" s="1"/>
     </row>
-    <row r="234" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>8</v>
       </c>
@@ -8510,7 +8656,7 @@
       <c r="Y234" s="1"/>
       <c r="Z234" s="1"/>
     </row>
-    <row r="235" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>9</v>
       </c>
@@ -8540,7 +8686,7 @@
       <c r="Y235" s="1"/>
       <c r="Z235" s="1"/>
     </row>
-    <row r="236" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>10</v>
       </c>
@@ -8570,7 +8716,7 @@
       <c r="Y236" s="1"/>
       <c r="Z236" s="1"/>
     </row>
-    <row r="237" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>11</v>
       </c>
@@ -8600,7 +8746,7 @@
       <c r="Y237" s="1"/>
       <c r="Z237" s="1"/>
     </row>
-    <row r="238" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>12</v>
       </c>
@@ -8630,7 +8776,7 @@
       <c r="Y238" s="1"/>
       <c r="Z238" s="1"/>
     </row>
-    <row r="239" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>13</v>
       </c>
@@ -8660,7 +8806,7 @@
       <c r="Y239" s="1"/>
       <c r="Z239" s="1"/>
     </row>
-    <row r="240" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>14</v>
       </c>
@@ -8690,7 +8836,7 @@
       <c r="Y240" s="1"/>
       <c r="Z240" s="1"/>
     </row>
-    <row r="241" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>15</v>
       </c>
@@ -8720,7 +8866,7 @@
       <c r="Y241" s="1"/>
       <c r="Z241" s="1"/>
     </row>
-    <row r="242" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>16</v>
       </c>
@@ -8750,7 +8896,7 @@
       <c r="Y242" s="1"/>
       <c r="Z242" s="1"/>
     </row>
-    <row r="243" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>17</v>
       </c>
@@ -8780,7 +8926,7 @@
       <c r="Y243" s="1"/>
       <c r="Z243" s="1"/>
     </row>
-    <row r="244" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>18</v>
       </c>
@@ -8810,7 +8956,7 @@
       <c r="Y244" s="1"/>
       <c r="Z244" s="1"/>
     </row>
-    <row r="245" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8838,7 +8984,7 @@
       <c r="Y245" s="1"/>
       <c r="Z245" s="1"/>
     </row>
-    <row r="246" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="14" t="s">
         <v>36</v>
       </c>
@@ -8868,7 +9014,7 @@
       <c r="Y246" s="1"/>
       <c r="Z246" s="1"/>
     </row>
-    <row r="247" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>2</v>
       </c>
@@ -8908,7 +9054,7 @@
       <c r="Y247" s="1"/>
       <c r="Z247" s="1"/>
     </row>
-    <row r="248" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>8</v>
       </c>
@@ -8938,7 +9084,7 @@
       <c r="Y248" s="1"/>
       <c r="Z248" s="1"/>
     </row>
-    <row r="249" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>9</v>
       </c>
@@ -8968,7 +9114,7 @@
       <c r="Y249" s="1"/>
       <c r="Z249" s="1"/>
     </row>
-    <row r="250" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>10</v>
       </c>
@@ -8998,7 +9144,7 @@
       <c r="Y250" s="1"/>
       <c r="Z250" s="1"/>
     </row>
-    <row r="251" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>11</v>
       </c>
@@ -9028,7 +9174,7 @@
       <c r="Y251" s="1"/>
       <c r="Z251" s="1"/>
     </row>
-    <row r="252" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>12</v>
       </c>
@@ -9058,7 +9204,7 @@
       <c r="Y252" s="1"/>
       <c r="Z252" s="1"/>
     </row>
-    <row r="253" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>13</v>
       </c>
@@ -9088,7 +9234,7 @@
       <c r="Y253" s="1"/>
       <c r="Z253" s="1"/>
     </row>
-    <row r="254" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>14</v>
       </c>
@@ -9118,7 +9264,7 @@
       <c r="Y254" s="1"/>
       <c r="Z254" s="1"/>
     </row>
-    <row r="255" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>15</v>
       </c>
@@ -9148,7 +9294,7 @@
       <c r="Y255" s="1"/>
       <c r="Z255" s="1"/>
     </row>
-    <row r="256" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>16</v>
       </c>
@@ -9178,7 +9324,7 @@
       <c r="Y256" s="1"/>
       <c r="Z256" s="1"/>
     </row>
-    <row r="257" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>17</v>
       </c>
@@ -9208,7 +9354,7 @@
       <c r="Y257" s="1"/>
       <c r="Z257" s="1"/>
     </row>
-    <row r="258" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>18</v>
       </c>
@@ -9238,7 +9384,7 @@
       <c r="Y258" s="1"/>
       <c r="Z258" s="1"/>
     </row>
-    <row r="259" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9266,7 +9412,7 @@
       <c r="Y259" s="1"/>
       <c r="Z259" s="1"/>
     </row>
-    <row r="260" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="14" t="s">
         <v>37</v>
       </c>
@@ -9296,7 +9442,7 @@
       <c r="Y260" s="1"/>
       <c r="Z260" s="1"/>
     </row>
-    <row r="261" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>2</v>
       </c>
@@ -9336,7 +9482,7 @@
       <c r="Y261" s="1"/>
       <c r="Z261" s="1"/>
     </row>
-    <row r="262" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>8</v>
       </c>
@@ -9366,7 +9512,7 @@
       <c r="Y262" s="1"/>
       <c r="Z262" s="1"/>
     </row>
-    <row r="263" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>9</v>
       </c>
@@ -9396,7 +9542,7 @@
       <c r="Y263" s="1"/>
       <c r="Z263" s="1"/>
     </row>
-    <row r="264" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>10</v>
       </c>
@@ -9426,7 +9572,7 @@
       <c r="Y264" s="1"/>
       <c r="Z264" s="1"/>
     </row>
-    <row r="265" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>11</v>
       </c>
@@ -9456,7 +9602,7 @@
       <c r="Y265" s="1"/>
       <c r="Z265" s="1"/>
     </row>
-    <row r="266" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>12</v>
       </c>
@@ -9486,7 +9632,7 @@
       <c r="Y266" s="1"/>
       <c r="Z266" s="1"/>
     </row>
-    <row r="267" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>13</v>
       </c>
@@ -9516,7 +9662,7 @@
       <c r="Y267" s="1"/>
       <c r="Z267" s="1"/>
     </row>
-    <row r="268" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>14</v>
       </c>
@@ -9546,7 +9692,7 @@
       <c r="Y268" s="1"/>
       <c r="Z268" s="1"/>
     </row>
-    <row r="269" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>15</v>
       </c>
@@ -9576,7 +9722,7 @@
       <c r="Y269" s="1"/>
       <c r="Z269" s="1"/>
     </row>
-    <row r="270" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>16</v>
       </c>
@@ -9606,7 +9752,7 @@
       <c r="Y270" s="1"/>
       <c r="Z270" s="1"/>
     </row>
-    <row r="271" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>17</v>
       </c>
@@ -9636,12 +9782,12 @@
       <c r="Y271" s="1"/>
       <c r="Z271" s="1"/>
     </row>
-    <row r="272" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A272" s="18" t="s">
+    <row r="272" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B272" s="19"/>
-      <c r="C272" s="20"/>
+      <c r="B272" s="26"/>
+      <c r="C272" s="27"/>
       <c r="D272" s="5"/>
       <c r="E272" s="5"/>
       <c r="F272" s="1"/>
@@ -9666,7 +9812,7 @@
       <c r="Y272" s="1"/>
       <c r="Z272" s="1"/>
     </row>
-    <row r="273" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9694,7 +9840,7 @@
       <c r="Y273" s="1"/>
       <c r="Z273" s="1"/>
     </row>
-    <row r="274" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="14" t="s">
         <v>38</v>
       </c>
@@ -9724,7 +9870,7 @@
       <c r="Y274" s="1"/>
       <c r="Z274" s="1"/>
     </row>
-    <row r="275" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>2</v>
       </c>
@@ -9764,7 +9910,7 @@
       <c r="Y275" s="1"/>
       <c r="Z275" s="1"/>
     </row>
-    <row r="276" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>8</v>
       </c>
@@ -9794,7 +9940,7 @@
       <c r="Y276" s="1"/>
       <c r="Z276" s="1"/>
     </row>
-    <row r="277" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>9</v>
       </c>
@@ -9824,7 +9970,7 @@
       <c r="Y277" s="1"/>
       <c r="Z277" s="1"/>
     </row>
-    <row r="278" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>10</v>
       </c>
@@ -9854,7 +10000,7 @@
       <c r="Y278" s="1"/>
       <c r="Z278" s="1"/>
     </row>
-    <row r="279" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>11</v>
       </c>
@@ -9884,7 +10030,7 @@
       <c r="Y279" s="1"/>
       <c r="Z279" s="1"/>
     </row>
-    <row r="280" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>12</v>
       </c>
@@ -9914,7 +10060,7 @@
       <c r="Y280" s="1"/>
       <c r="Z280" s="1"/>
     </row>
-    <row r="281" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
         <v>13</v>
       </c>
@@ -9944,7 +10090,7 @@
       <c r="Y281" s="1"/>
       <c r="Z281" s="1"/>
     </row>
-    <row r="282" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>14</v>
       </c>
@@ -9974,7 +10120,7 @@
       <c r="Y282" s="1"/>
       <c r="Z282" s="1"/>
     </row>
-    <row r="283" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>15</v>
       </c>
@@ -10004,7 +10150,7 @@
       <c r="Y283" s="1"/>
       <c r="Z283" s="1"/>
     </row>
-    <row r="284" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>16</v>
       </c>
@@ -10034,7 +10180,7 @@
       <c r="Y284" s="1"/>
       <c r="Z284" s="1"/>
     </row>
-    <row r="285" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>17</v>
       </c>
@@ -10064,12 +10210,12 @@
       <c r="Y285" s="1"/>
       <c r="Z285" s="1"/>
     </row>
-    <row r="286" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A286" s="18" t="s">
+    <row r="286" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B286" s="19"/>
-      <c r="C286" s="20"/>
+      <c r="B286" s="26"/>
+      <c r="C286" s="27"/>
       <c r="D286" s="5"/>
       <c r="E286" s="5"/>
       <c r="F286" s="1"/>
@@ -10094,7 +10240,7 @@
       <c r="Y286" s="1"/>
       <c r="Z286" s="1"/>
     </row>
-    <row r="287" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -10122,7 +10268,7 @@
       <c r="Y287" s="1"/>
       <c r="Z287" s="1"/>
     </row>
-    <row r="288" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="14" t="s">
         <v>39</v>
       </c>
@@ -10152,7 +10298,7 @@
       <c r="Y288" s="1"/>
       <c r="Z288" s="1"/>
     </row>
-    <row r="289" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>2</v>
       </c>
@@ -10192,7 +10338,7 @@
       <c r="Y289" s="1"/>
       <c r="Z289" s="1"/>
     </row>
-    <row r="290" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>8</v>
       </c>
@@ -10222,7 +10368,7 @@
       <c r="Y290" s="1"/>
       <c r="Z290" s="1"/>
     </row>
-    <row r="291" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>9</v>
       </c>
@@ -10252,7 +10398,7 @@
       <c r="Y291" s="1"/>
       <c r="Z291" s="1"/>
     </row>
-    <row r="292" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>10</v>
       </c>
@@ -10282,7 +10428,7 @@
       <c r="Y292" s="1"/>
       <c r="Z292" s="1"/>
     </row>
-    <row r="293" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>11</v>
       </c>
@@ -10312,7 +10458,7 @@
       <c r="Y293" s="1"/>
       <c r="Z293" s="1"/>
     </row>
-    <row r="294" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>12</v>
       </c>
@@ -10342,7 +10488,7 @@
       <c r="Y294" s="1"/>
       <c r="Z294" s="1"/>
     </row>
-    <row r="295" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>13</v>
       </c>
@@ -10372,7 +10518,7 @@
       <c r="Y295" s="1"/>
       <c r="Z295" s="1"/>
     </row>
-    <row r="296" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>14</v>
       </c>
@@ -10402,7 +10548,7 @@
       <c r="Y296" s="1"/>
       <c r="Z296" s="1"/>
     </row>
-    <row r="297" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>15</v>
       </c>
@@ -10432,7 +10578,7 @@
       <c r="Y297" s="1"/>
       <c r="Z297" s="1"/>
     </row>
-    <row r="298" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>16</v>
       </c>
@@ -10462,7 +10608,7 @@
       <c r="Y298" s="1"/>
       <c r="Z298" s="1"/>
     </row>
-    <row r="299" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>17</v>
       </c>
@@ -10492,12 +10638,12 @@
       <c r="Y299" s="1"/>
       <c r="Z299" s="1"/>
     </row>
-    <row r="300" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A300" s="18" t="s">
+    <row r="300" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A300" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B300" s="19"/>
-      <c r="C300" s="20"/>
+      <c r="B300" s="26"/>
+      <c r="C300" s="27"/>
       <c r="D300" s="5"/>
       <c r="E300" s="5"/>
       <c r="F300" s="1"/>
@@ -10522,7 +10668,7 @@
       <c r="Y300" s="1"/>
       <c r="Z300" s="1"/>
     </row>
-    <row r="301" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -10550,7 +10696,7 @@
       <c r="Y301" s="1"/>
       <c r="Z301" s="1"/>
     </row>
-    <row r="302" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="14" t="s">
         <v>40</v>
       </c>
@@ -10580,7 +10726,7 @@
       <c r="Y302" s="1"/>
       <c r="Z302" s="1"/>
     </row>
-    <row r="303" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>2</v>
       </c>
@@ -10620,7 +10766,7 @@
       <c r="Y303" s="1"/>
       <c r="Z303" s="1"/>
     </row>
-    <row r="304" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>8</v>
       </c>
@@ -10650,7 +10796,7 @@
       <c r="Y304" s="1"/>
       <c r="Z304" s="1"/>
     </row>
-    <row r="305" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>9</v>
       </c>
@@ -10680,7 +10826,7 @@
       <c r="Y305" s="1"/>
       <c r="Z305" s="1"/>
     </row>
-    <row r="306" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>10</v>
       </c>
@@ -10710,7 +10856,7 @@
       <c r="Y306" s="1"/>
       <c r="Z306" s="1"/>
     </row>
-    <row r="307" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>11</v>
       </c>
@@ -10740,7 +10886,7 @@
       <c r="Y307" s="1"/>
       <c r="Z307" s="1"/>
     </row>
-    <row r="308" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>12</v>
       </c>
@@ -10770,7 +10916,7 @@
       <c r="Y308" s="1"/>
       <c r="Z308" s="1"/>
     </row>
-    <row r="309" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>13</v>
       </c>
@@ -10800,7 +10946,7 @@
       <c r="Y309" s="1"/>
       <c r="Z309" s="1"/>
     </row>
-    <row r="310" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>14</v>
       </c>
@@ -10830,7 +10976,7 @@
       <c r="Y310" s="1"/>
       <c r="Z310" s="1"/>
     </row>
-    <row r="311" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>15</v>
       </c>
@@ -10860,7 +11006,7 @@
       <c r="Y311" s="1"/>
       <c r="Z311" s="1"/>
     </row>
-    <row r="312" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>16</v>
       </c>
@@ -10890,7 +11036,7 @@
       <c r="Y312" s="1"/>
       <c r="Z312" s="1"/>
     </row>
-    <row r="313" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>17</v>
       </c>
@@ -10920,12 +11066,12 @@
       <c r="Y313" s="1"/>
       <c r="Z313" s="1"/>
     </row>
-    <row r="314" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A314" s="18" t="s">
+    <row r="314" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A314" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B314" s="19"/>
-      <c r="C314" s="20"/>
+      <c r="B314" s="26"/>
+      <c r="C314" s="27"/>
       <c r="D314" s="5"/>
       <c r="E314" s="5"/>
       <c r="F314" s="1"/>
@@ -10950,7 +11096,7 @@
       <c r="Y314" s="1"/>
       <c r="Z314" s="1"/>
     </row>
-    <row r="315" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10978,7 +11124,7 @@
       <c r="Y315" s="1"/>
       <c r="Z315" s="1"/>
     </row>
-    <row r="316" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="14" t="s">
         <v>41</v>
       </c>
@@ -11008,7 +11154,7 @@
       <c r="Y316" s="1"/>
       <c r="Z316" s="1"/>
     </row>
-    <row r="317" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>2</v>
       </c>
@@ -11048,7 +11194,7 @@
       <c r="Y317" s="1"/>
       <c r="Z317" s="1"/>
     </row>
-    <row r="318" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>8</v>
       </c>
@@ -11078,7 +11224,7 @@
       <c r="Y318" s="1"/>
       <c r="Z318" s="1"/>
     </row>
-    <row r="319" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>9</v>
       </c>
@@ -11108,7 +11254,7 @@
       <c r="Y319" s="1"/>
       <c r="Z319" s="1"/>
     </row>
-    <row r="320" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>10</v>
       </c>
@@ -11138,7 +11284,7 @@
       <c r="Y320" s="1"/>
       <c r="Z320" s="1"/>
     </row>
-    <row r="321" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>11</v>
       </c>
@@ -11168,7 +11314,7 @@
       <c r="Y321" s="1"/>
       <c r="Z321" s="1"/>
     </row>
-    <row r="322" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4" t="s">
         <v>12</v>
       </c>
@@ -11198,7 +11344,7 @@
       <c r="Y322" s="1"/>
       <c r="Z322" s="1"/>
     </row>
-    <row r="323" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="4" t="s">
         <v>13</v>
       </c>
@@ -11228,7 +11374,7 @@
       <c r="Y323" s="1"/>
       <c r="Z323" s="1"/>
     </row>
-    <row r="324" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="4" t="s">
         <v>14</v>
       </c>
@@ -11258,7 +11404,7 @@
       <c r="Y324" s="1"/>
       <c r="Z324" s="1"/>
     </row>
-    <row r="325" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="4" t="s">
         <v>15</v>
       </c>
@@ -11288,7 +11434,7 @@
       <c r="Y325" s="1"/>
       <c r="Z325" s="1"/>
     </row>
-    <row r="326" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4" t="s">
         <v>16</v>
       </c>
@@ -11318,7 +11464,7 @@
       <c r="Y326" s="1"/>
       <c r="Z326" s="1"/>
     </row>
-    <row r="327" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
         <v>17</v>
       </c>
@@ -11348,12 +11494,12 @@
       <c r="Y327" s="1"/>
       <c r="Z327" s="1"/>
     </row>
-    <row r="328" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A328" s="18" t="s">
+    <row r="328" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A328" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B328" s="19"/>
-      <c r="C328" s="20"/>
+      <c r="B328" s="26"/>
+      <c r="C328" s="27"/>
       <c r="D328" s="5"/>
       <c r="E328" s="5"/>
       <c r="F328" s="1"/>
@@ -11378,7 +11524,7 @@
       <c r="Y328" s="1"/>
       <c r="Z328" s="1"/>
     </row>
-    <row r="329" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -11406,7 +11552,7 @@
       <c r="Y329" s="1"/>
       <c r="Z329" s="1"/>
     </row>
-    <row r="330" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="14" t="s">
         <v>42</v>
       </c>
@@ -11436,7 +11582,7 @@
       <c r="Y330" s="1"/>
       <c r="Z330" s="1"/>
     </row>
-    <row r="331" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>2</v>
       </c>
@@ -11476,7 +11622,7 @@
       <c r="Y331" s="1"/>
       <c r="Z331" s="1"/>
     </row>
-    <row r="332" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
         <v>8</v>
       </c>
@@ -11506,7 +11652,7 @@
       <c r="Y332" s="1"/>
       <c r="Z332" s="1"/>
     </row>
-    <row r="333" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
         <v>9</v>
       </c>
@@ -11536,7 +11682,7 @@
       <c r="Y333" s="1"/>
       <c r="Z333" s="1"/>
     </row>
-    <row r="334" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
         <v>10</v>
       </c>
@@ -11566,7 +11712,7 @@
       <c r="Y334" s="1"/>
       <c r="Z334" s="1"/>
     </row>
-    <row r="335" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
         <v>11</v>
       </c>
@@ -11596,7 +11742,7 @@
       <c r="Y335" s="1"/>
       <c r="Z335" s="1"/>
     </row>
-    <row r="336" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
         <v>12</v>
       </c>
@@ -11626,7 +11772,7 @@
       <c r="Y336" s="1"/>
       <c r="Z336" s="1"/>
     </row>
-    <row r="337" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
         <v>13</v>
       </c>
@@ -11656,7 +11802,7 @@
       <c r="Y337" s="1"/>
       <c r="Z337" s="1"/>
     </row>
-    <row r="338" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
         <v>14</v>
       </c>
@@ -11686,7 +11832,7 @@
       <c r="Y338" s="1"/>
       <c r="Z338" s="1"/>
     </row>
-    <row r="339" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
         <v>15</v>
       </c>
@@ -11716,7 +11862,7 @@
       <c r="Y339" s="1"/>
       <c r="Z339" s="1"/>
     </row>
-    <row r="340" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
         <v>16</v>
       </c>
@@ -11746,7 +11892,7 @@
       <c r="Y340" s="1"/>
       <c r="Z340" s="1"/>
     </row>
-    <row r="341" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
         <v>17</v>
       </c>
@@ -11776,7 +11922,7 @@
       <c r="Y341" s="1"/>
       <c r="Z341" s="1"/>
     </row>
-    <row r="342" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
         <v>18</v>
       </c>
@@ -11806,7 +11952,7 @@
       <c r="Y342" s="1"/>
       <c r="Z342" s="1"/>
     </row>
-    <row r="343" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11834,7 +11980,7 @@
       <c r="Y343" s="1"/>
       <c r="Z343" s="1"/>
     </row>
-    <row r="344" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11862,7 +12008,7 @@
       <c r="Y344" s="1"/>
       <c r="Z344" s="1"/>
     </row>
-    <row r="345" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11890,7 +12036,7 @@
       <c r="Y345" s="1"/>
       <c r="Z345" s="1"/>
     </row>
-    <row r="346" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11918,7 +12064,7 @@
       <c r="Y346" s="1"/>
       <c r="Z346" s="1"/>
     </row>
-    <row r="347" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11946,7 +12092,7 @@
       <c r="Y347" s="1"/>
       <c r="Z347" s="1"/>
     </row>
-    <row r="348" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11974,7 +12120,7 @@
       <c r="Y348" s="1"/>
       <c r="Z348" s="1"/>
     </row>
-    <row r="349" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -12002,7 +12148,7 @@
       <c r="Y349" s="1"/>
       <c r="Z349" s="1"/>
     </row>
-    <row r="350" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -12030,7 +12176,7 @@
       <c r="Y350" s="1"/>
       <c r="Z350" s="1"/>
     </row>
-    <row r="351" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -12058,7 +12204,7 @@
       <c r="Y351" s="1"/>
       <c r="Z351" s="1"/>
     </row>
-    <row r="352" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -12086,7 +12232,7 @@
       <c r="Y352" s="1"/>
       <c r="Z352" s="1"/>
     </row>
-    <row r="353" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -12114,7 +12260,7 @@
       <c r="Y353" s="1"/>
       <c r="Z353" s="1"/>
     </row>
-    <row r="354" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -12142,7 +12288,7 @@
       <c r="Y354" s="1"/>
       <c r="Z354" s="1"/>
     </row>
-    <row r="355" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -12170,7 +12316,7 @@
       <c r="Y355" s="1"/>
       <c r="Z355" s="1"/>
     </row>
-    <row r="356" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -12198,7 +12344,7 @@
       <c r="Y356" s="1"/>
       <c r="Z356" s="1"/>
     </row>
-    <row r="357" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -12226,7 +12372,7 @@
       <c r="Y357" s="1"/>
       <c r="Z357" s="1"/>
     </row>
-    <row r="358" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -12254,7 +12400,7 @@
       <c r="Y358" s="1"/>
       <c r="Z358" s="1"/>
     </row>
-    <row r="359" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -12282,7 +12428,7 @@
       <c r="Y359" s="1"/>
       <c r="Z359" s="1"/>
     </row>
-    <row r="360" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -12310,7 +12456,7 @@
       <c r="Y360" s="1"/>
       <c r="Z360" s="1"/>
     </row>
-    <row r="361" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -12338,7 +12484,7 @@
       <c r="Y361" s="1"/>
       <c r="Z361" s="1"/>
     </row>
-    <row r="362" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12366,7 +12512,7 @@
       <c r="Y362" s="1"/>
       <c r="Z362" s="1"/>
     </row>
-    <row r="363" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12394,7 +12540,7 @@
       <c r="Y363" s="1"/>
       <c r="Z363" s="1"/>
     </row>
-    <row r="364" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12422,7 +12568,7 @@
       <c r="Y364" s="1"/>
       <c r="Z364" s="1"/>
     </row>
-    <row r="365" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12450,7 +12596,7 @@
       <c r="Y365" s="1"/>
       <c r="Z365" s="1"/>
     </row>
-    <row r="366" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -12478,7 +12624,7 @@
       <c r="Y366" s="1"/>
       <c r="Z366" s="1"/>
     </row>
-    <row r="367" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -12506,7 +12652,7 @@
       <c r="Y367" s="1"/>
       <c r="Z367" s="1"/>
     </row>
-    <row r="368" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -12534,7 +12680,7 @@
       <c r="Y368" s="1"/>
       <c r="Z368" s="1"/>
     </row>
-    <row r="369" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12562,7 +12708,7 @@
       <c r="Y369" s="1"/>
       <c r="Z369" s="1"/>
     </row>
-    <row r="370" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12590,7 +12736,7 @@
       <c r="Y370" s="1"/>
       <c r="Z370" s="1"/>
     </row>
-    <row r="371" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12618,7 +12764,7 @@
       <c r="Y371" s="1"/>
       <c r="Z371" s="1"/>
     </row>
-    <row r="372" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12646,7 +12792,7 @@
       <c r="Y372" s="1"/>
       <c r="Z372" s="1"/>
     </row>
-    <row r="373" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12674,7 +12820,7 @@
       <c r="Y373" s="1"/>
       <c r="Z373" s="1"/>
     </row>
-    <row r="374" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12702,7 +12848,7 @@
       <c r="Y374" s="1"/>
       <c r="Z374" s="1"/>
     </row>
-    <row r="375" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12730,7 +12876,7 @@
       <c r="Y375" s="1"/>
       <c r="Z375" s="1"/>
     </row>
-    <row r="376" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12758,7 +12904,7 @@
       <c r="Y376" s="1"/>
       <c r="Z376" s="1"/>
     </row>
-    <row r="377" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12786,7 +12932,7 @@
       <c r="Y377" s="1"/>
       <c r="Z377" s="1"/>
     </row>
-    <row r="378" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12814,7 +12960,7 @@
       <c r="Y378" s="1"/>
       <c r="Z378" s="1"/>
     </row>
-    <row r="379" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12842,7 +12988,7 @@
       <c r="Y379" s="1"/>
       <c r="Z379" s="1"/>
     </row>
-    <row r="380" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12870,7 +13016,7 @@
       <c r="Y380" s="1"/>
       <c r="Z380" s="1"/>
     </row>
-    <row r="381" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12898,7 +13044,7 @@
       <c r="Y381" s="1"/>
       <c r="Z381" s="1"/>
     </row>
-    <row r="382" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -12926,7 +13072,7 @@
       <c r="Y382" s="1"/>
       <c r="Z382" s="1"/>
     </row>
-    <row r="383" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -12954,7 +13100,7 @@
       <c r="Y383" s="1"/>
       <c r="Z383" s="1"/>
     </row>
-    <row r="384" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -12982,7 +13128,7 @@
       <c r="Y384" s="1"/>
       <c r="Z384" s="1"/>
     </row>
-    <row r="385" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -13010,7 +13156,7 @@
       <c r="Y385" s="1"/>
       <c r="Z385" s="1"/>
     </row>
-    <row r="386" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -13038,7 +13184,7 @@
       <c r="Y386" s="1"/>
       <c r="Z386" s="1"/>
     </row>
-    <row r="387" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -13066,7 +13212,7 @@
       <c r="Y387" s="1"/>
       <c r="Z387" s="1"/>
     </row>
-    <row r="388" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -13094,7 +13240,7 @@
       <c r="Y388" s="1"/>
       <c r="Z388" s="1"/>
     </row>
-    <row r="389" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -13122,7 +13268,7 @@
       <c r="Y389" s="1"/>
       <c r="Z389" s="1"/>
     </row>
-    <row r="390" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -13150,7 +13296,7 @@
       <c r="Y390" s="1"/>
       <c r="Z390" s="1"/>
     </row>
-    <row r="391" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -13178,7 +13324,7 @@
       <c r="Y391" s="1"/>
       <c r="Z391" s="1"/>
     </row>
-    <row r="392" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -13206,7 +13352,7 @@
       <c r="Y392" s="1"/>
       <c r="Z392" s="1"/>
     </row>
-    <row r="393" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -13234,7 +13380,7 @@
       <c r="Y393" s="1"/>
       <c r="Z393" s="1"/>
     </row>
-    <row r="394" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13262,7 +13408,7 @@
       <c r="Y394" s="1"/>
       <c r="Z394" s="1"/>
     </row>
-    <row r="395" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13290,7 +13436,7 @@
       <c r="Y395" s="1"/>
       <c r="Z395" s="1"/>
     </row>
-    <row r="396" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13318,7 +13464,7 @@
       <c r="Y396" s="1"/>
       <c r="Z396" s="1"/>
     </row>
-    <row r="397" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13346,7 +13492,7 @@
       <c r="Y397" s="1"/>
       <c r="Z397" s="1"/>
     </row>
-    <row r="398" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13374,7 +13520,7 @@
       <c r="Y398" s="1"/>
       <c r="Z398" s="1"/>
     </row>
-    <row r="399" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -13402,7 +13548,7 @@
       <c r="Y399" s="1"/>
       <c r="Z399" s="1"/>
     </row>
-    <row r="400" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -13430,7 +13576,7 @@
       <c r="Y400" s="1"/>
       <c r="Z400" s="1"/>
     </row>
-    <row r="401" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -13458,7 +13604,7 @@
       <c r="Y401" s="1"/>
       <c r="Z401" s="1"/>
     </row>
-    <row r="402" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13486,7 +13632,7 @@
       <c r="Y402" s="1"/>
       <c r="Z402" s="1"/>
     </row>
-    <row r="403" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13514,7 +13660,7 @@
       <c r="Y403" s="1"/>
       <c r="Z403" s="1"/>
     </row>
-    <row r="404" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13542,7 +13688,7 @@
       <c r="Y404" s="1"/>
       <c r="Z404" s="1"/>
     </row>
-    <row r="405" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13570,7 +13716,7 @@
       <c r="Y405" s="1"/>
       <c r="Z405" s="1"/>
     </row>
-    <row r="406" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13598,7 +13744,7 @@
       <c r="Y406" s="1"/>
       <c r="Z406" s="1"/>
     </row>
-    <row r="407" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13626,7 +13772,7 @@
       <c r="Y407" s="1"/>
       <c r="Z407" s="1"/>
     </row>
-    <row r="408" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13654,7 +13800,7 @@
       <c r="Y408" s="1"/>
       <c r="Z408" s="1"/>
     </row>
-    <row r="409" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13682,7 +13828,7 @@
       <c r="Y409" s="1"/>
       <c r="Z409" s="1"/>
     </row>
-    <row r="410" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13710,7 +13856,7 @@
       <c r="Y410" s="1"/>
       <c r="Z410" s="1"/>
     </row>
-    <row r="411" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13738,7 +13884,7 @@
       <c r="Y411" s="1"/>
       <c r="Z411" s="1"/>
     </row>
-    <row r="412" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13766,7 +13912,7 @@
       <c r="Y412" s="1"/>
       <c r="Z412" s="1"/>
     </row>
-    <row r="413" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13794,7 +13940,7 @@
       <c r="Y413" s="1"/>
       <c r="Z413" s="1"/>
     </row>
-    <row r="414" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -13822,7 +13968,7 @@
       <c r="Y414" s="1"/>
       <c r="Z414" s="1"/>
     </row>
-    <row r="415" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -13850,7 +13996,7 @@
       <c r="Y415" s="1"/>
       <c r="Z415" s="1"/>
     </row>
-    <row r="416" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -13878,7 +14024,7 @@
       <c r="Y416" s="1"/>
       <c r="Z416" s="1"/>
     </row>
-    <row r="417" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -13906,7 +14052,7 @@
       <c r="Y417" s="1"/>
       <c r="Z417" s="1"/>
     </row>
-    <row r="418" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -13934,7 +14080,7 @@
       <c r="Y418" s="1"/>
       <c r="Z418" s="1"/>
     </row>
-    <row r="419" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -13962,7 +14108,7 @@
       <c r="Y419" s="1"/>
       <c r="Z419" s="1"/>
     </row>
-    <row r="420" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -13990,7 +14136,7 @@
       <c r="Y420" s="1"/>
       <c r="Z420" s="1"/>
     </row>
-    <row r="421" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -14018,7 +14164,7 @@
       <c r="Y421" s="1"/>
       <c r="Z421" s="1"/>
     </row>
-    <row r="422" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -14046,7 +14192,7 @@
       <c r="Y422" s="1"/>
       <c r="Z422" s="1"/>
     </row>
-    <row r="423" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -14074,7 +14220,7 @@
       <c r="Y423" s="1"/>
       <c r="Z423" s="1"/>
     </row>
-    <row r="424" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -14102,7 +14248,7 @@
       <c r="Y424" s="1"/>
       <c r="Z424" s="1"/>
     </row>
-    <row r="425" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -14130,7 +14276,7 @@
       <c r="Y425" s="1"/>
       <c r="Z425" s="1"/>
     </row>
-    <row r="426" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -14158,7 +14304,7 @@
       <c r="Y426" s="1"/>
       <c r="Z426" s="1"/>
     </row>
-    <row r="427" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -14186,7 +14332,7 @@
       <c r="Y427" s="1"/>
       <c r="Z427" s="1"/>
     </row>
-    <row r="428" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -14214,7 +14360,7 @@
       <c r="Y428" s="1"/>
       <c r="Z428" s="1"/>
     </row>
-    <row r="429" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -14242,7 +14388,7 @@
       <c r="Y429" s="1"/>
       <c r="Z429" s="1"/>
     </row>
-    <row r="430" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -14270,7 +14416,7 @@
       <c r="Y430" s="1"/>
       <c r="Z430" s="1"/>
     </row>
-    <row r="431" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -14298,7 +14444,7 @@
       <c r="Y431" s="1"/>
       <c r="Z431" s="1"/>
     </row>
-    <row r="432" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -14326,7 +14472,7 @@
       <c r="Y432" s="1"/>
       <c r="Z432" s="1"/>
     </row>
-    <row r="433" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -14354,7 +14500,7 @@
       <c r="Y433" s="1"/>
       <c r="Z433" s="1"/>
     </row>
-    <row r="434" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -14382,7 +14528,7 @@
       <c r="Y434" s="1"/>
       <c r="Z434" s="1"/>
     </row>
-    <row r="435" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -14410,7 +14556,7 @@
       <c r="Y435" s="1"/>
       <c r="Z435" s="1"/>
     </row>
-    <row r="436" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14438,7 +14584,7 @@
       <c r="Y436" s="1"/>
       <c r="Z436" s="1"/>
     </row>
-    <row r="437" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14466,7 +14612,7 @@
       <c r="Y437" s="1"/>
       <c r="Z437" s="1"/>
     </row>
-    <row r="438" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14494,7 +14640,7 @@
       <c r="Y438" s="1"/>
       <c r="Z438" s="1"/>
     </row>
-    <row r="439" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14522,7 +14668,7 @@
       <c r="Y439" s="1"/>
       <c r="Z439" s="1"/>
     </row>
-    <row r="440" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14550,7 +14696,7 @@
       <c r="Y440" s="1"/>
       <c r="Z440" s="1"/>
     </row>
-    <row r="441" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14578,7 +14724,7 @@
       <c r="Y441" s="1"/>
       <c r="Z441" s="1"/>
     </row>
-    <row r="442" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14606,7 +14752,7 @@
       <c r="Y442" s="1"/>
       <c r="Z442" s="1"/>
     </row>
-    <row r="443" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14634,7 +14780,7 @@
       <c r="Y443" s="1"/>
       <c r="Z443" s="1"/>
     </row>
-    <row r="444" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14662,7 +14808,7 @@
       <c r="Y444" s="1"/>
       <c r="Z444" s="1"/>
     </row>
-    <row r="445" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14690,7 +14836,7 @@
       <c r="Y445" s="1"/>
       <c r="Z445" s="1"/>
     </row>
-    <row r="446" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -14718,7 +14864,7 @@
       <c r="Y446" s="1"/>
       <c r="Z446" s="1"/>
     </row>
-    <row r="447" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -14746,7 +14892,7 @@
       <c r="Y447" s="1"/>
       <c r="Z447" s="1"/>
     </row>
-    <row r="448" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -14774,7 +14920,7 @@
       <c r="Y448" s="1"/>
       <c r="Z448" s="1"/>
     </row>
-    <row r="449" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -14802,7 +14948,7 @@
       <c r="Y449" s="1"/>
       <c r="Z449" s="1"/>
     </row>
-    <row r="450" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -14830,7 +14976,7 @@
       <c r="Y450" s="1"/>
       <c r="Z450" s="1"/>
     </row>
-    <row r="451" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -14858,7 +15004,7 @@
       <c r="Y451" s="1"/>
       <c r="Z451" s="1"/>
     </row>
-    <row r="452" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -14886,7 +15032,7 @@
       <c r="Y452" s="1"/>
       <c r="Z452" s="1"/>
     </row>
-    <row r="453" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -14914,7 +15060,7 @@
       <c r="Y453" s="1"/>
       <c r="Z453" s="1"/>
     </row>
-    <row r="454" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -14942,7 +15088,7 @@
       <c r="Y454" s="1"/>
       <c r="Z454" s="1"/>
     </row>
-    <row r="455" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -14970,7 +15116,7 @@
       <c r="Y455" s="1"/>
       <c r="Z455" s="1"/>
     </row>
-    <row r="456" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -14998,7 +15144,7 @@
       <c r="Y456" s="1"/>
       <c r="Z456" s="1"/>
     </row>
-    <row r="457" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -15026,7 +15172,7 @@
       <c r="Y457" s="1"/>
       <c r="Z457" s="1"/>
     </row>
-    <row r="458" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -15054,7 +15200,7 @@
       <c r="Y458" s="1"/>
       <c r="Z458" s="1"/>
     </row>
-    <row r="459" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -15082,7 +15228,7 @@
       <c r="Y459" s="1"/>
       <c r="Z459" s="1"/>
     </row>
-    <row r="460" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -15110,7 +15256,7 @@
       <c r="Y460" s="1"/>
       <c r="Z460" s="1"/>
     </row>
-    <row r="461" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -15138,7 +15284,7 @@
       <c r="Y461" s="1"/>
       <c r="Z461" s="1"/>
     </row>
-    <row r="462" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -15166,7 +15312,7 @@
       <c r="Y462" s="1"/>
       <c r="Z462" s="1"/>
     </row>
-    <row r="463" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -15194,7 +15340,7 @@
       <c r="Y463" s="1"/>
       <c r="Z463" s="1"/>
     </row>
-    <row r="464" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -15222,7 +15368,7 @@
       <c r="Y464" s="1"/>
       <c r="Z464" s="1"/>
     </row>
-    <row r="465" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -15250,7 +15396,7 @@
       <c r="Y465" s="1"/>
       <c r="Z465" s="1"/>
     </row>
-    <row r="466" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -15278,7 +15424,7 @@
       <c r="Y466" s="1"/>
       <c r="Z466" s="1"/>
     </row>
-    <row r="467" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -15306,7 +15452,7 @@
       <c r="Y467" s="1"/>
       <c r="Z467" s="1"/>
     </row>
-    <row r="468" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -15334,7 +15480,7 @@
       <c r="Y468" s="1"/>
       <c r="Z468" s="1"/>
     </row>
-    <row r="469" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15362,7 +15508,7 @@
       <c r="Y469" s="1"/>
       <c r="Z469" s="1"/>
     </row>
-    <row r="470" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15390,7 +15536,7 @@
       <c r="Y470" s="1"/>
       <c r="Z470" s="1"/>
     </row>
-    <row r="471" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15418,7 +15564,7 @@
       <c r="Y471" s="1"/>
       <c r="Z471" s="1"/>
     </row>
-    <row r="472" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15446,7 +15592,7 @@
       <c r="Y472" s="1"/>
       <c r="Z472" s="1"/>
     </row>
-    <row r="473" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15474,7 +15620,7 @@
       <c r="Y473" s="1"/>
       <c r="Z473" s="1"/>
     </row>
-    <row r="474" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15502,7 +15648,7 @@
       <c r="Y474" s="1"/>
       <c r="Z474" s="1"/>
     </row>
-    <row r="475" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15530,7 +15676,7 @@
       <c r="Y475" s="1"/>
       <c r="Z475" s="1"/>
     </row>
-    <row r="476" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15558,7 +15704,7 @@
       <c r="Y476" s="1"/>
       <c r="Z476" s="1"/>
     </row>
-    <row r="477" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15586,7 +15732,7 @@
       <c r="Y477" s="1"/>
       <c r="Z477" s="1"/>
     </row>
-    <row r="478" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -15614,7 +15760,7 @@
       <c r="Y478" s="1"/>
       <c r="Z478" s="1"/>
     </row>
-    <row r="479" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -15642,7 +15788,7 @@
       <c r="Y479" s="1"/>
       <c r="Z479" s="1"/>
     </row>
-    <row r="480" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -15670,7 +15816,7 @@
       <c r="Y480" s="1"/>
       <c r="Z480" s="1"/>
     </row>
-    <row r="481" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -15698,7 +15844,7 @@
       <c r="Y481" s="1"/>
       <c r="Z481" s="1"/>
     </row>
-    <row r="482" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -15726,7 +15872,7 @@
       <c r="Y482" s="1"/>
       <c r="Z482" s="1"/>
     </row>
-    <row r="483" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -15754,7 +15900,7 @@
       <c r="Y483" s="1"/>
       <c r="Z483" s="1"/>
     </row>
-    <row r="484" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -15782,7 +15928,7 @@
       <c r="Y484" s="1"/>
       <c r="Z484" s="1"/>
     </row>
-    <row r="485" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -15810,7 +15956,7 @@
       <c r="Y485" s="1"/>
       <c r="Z485" s="1"/>
     </row>
-    <row r="486" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -15838,7 +15984,7 @@
       <c r="Y486" s="1"/>
       <c r="Z486" s="1"/>
     </row>
-    <row r="487" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -15866,7 +16012,7 @@
       <c r="Y487" s="1"/>
       <c r="Z487" s="1"/>
     </row>
-    <row r="488" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -15894,7 +16040,7 @@
       <c r="Y488" s="1"/>
       <c r="Z488" s="1"/>
     </row>
-    <row r="489" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -15922,7 +16068,7 @@
       <c r="Y489" s="1"/>
       <c r="Z489" s="1"/>
     </row>
-    <row r="490" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -15950,7 +16096,7 @@
       <c r="Y490" s="1"/>
       <c r="Z490" s="1"/>
     </row>
-    <row r="491" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -15978,7 +16124,7 @@
       <c r="Y491" s="1"/>
       <c r="Z491" s="1"/>
     </row>
-    <row r="492" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -16006,7 +16152,7 @@
       <c r="Y492" s="1"/>
       <c r="Z492" s="1"/>
     </row>
-    <row r="493" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -16034,7 +16180,7 @@
       <c r="Y493" s="1"/>
       <c r="Z493" s="1"/>
     </row>
-    <row r="494" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -16062,7 +16208,7 @@
       <c r="Y494" s="1"/>
       <c r="Z494" s="1"/>
     </row>
-    <row r="495" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -16090,7 +16236,7 @@
       <c r="Y495" s="1"/>
       <c r="Z495" s="1"/>
     </row>
-    <row r="496" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -16118,7 +16264,7 @@
       <c r="Y496" s="1"/>
       <c r="Z496" s="1"/>
     </row>
-    <row r="497" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -16146,7 +16292,7 @@
       <c r="Y497" s="1"/>
       <c r="Z497" s="1"/>
     </row>
-    <row r="498" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -16174,7 +16320,7 @@
       <c r="Y498" s="1"/>
       <c r="Z498" s="1"/>
     </row>
-    <row r="499" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -16202,7 +16348,7 @@
       <c r="Y499" s="1"/>
       <c r="Z499" s="1"/>
     </row>
-    <row r="500" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -16230,7 +16376,7 @@
       <c r="Y500" s="1"/>
       <c r="Z500" s="1"/>
     </row>
-    <row r="501" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -16258,7 +16404,7 @@
       <c r="Y501" s="1"/>
       <c r="Z501" s="1"/>
     </row>
-    <row r="502" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -16286,7 +16432,7 @@
       <c r="Y502" s="1"/>
       <c r="Z502" s="1"/>
     </row>
-    <row r="503" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16314,7 +16460,7 @@
       <c r="Y503" s="1"/>
       <c r="Z503" s="1"/>
     </row>
-    <row r="504" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16342,7 +16488,7 @@
       <c r="Y504" s="1"/>
       <c r="Z504" s="1"/>
     </row>
-    <row r="505" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16370,7 +16516,7 @@
       <c r="Y505" s="1"/>
       <c r="Z505" s="1"/>
     </row>
-    <row r="506" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16398,7 +16544,7 @@
       <c r="Y506" s="1"/>
       <c r="Z506" s="1"/>
     </row>
-    <row r="507" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16426,7 +16572,7 @@
       <c r="Y507" s="1"/>
       <c r="Z507" s="1"/>
     </row>
-    <row r="508" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16454,7 +16600,7 @@
       <c r="Y508" s="1"/>
       <c r="Z508" s="1"/>
     </row>
-    <row r="509" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16482,7 +16628,7 @@
       <c r="Y509" s="1"/>
       <c r="Z509" s="1"/>
     </row>
-    <row r="510" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16510,7 +16656,7 @@
       <c r="Y510" s="1"/>
       <c r="Z510" s="1"/>
     </row>
-    <row r="511" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -16538,7 +16684,7 @@
       <c r="Y511" s="1"/>
       <c r="Z511" s="1"/>
     </row>
-    <row r="512" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -16566,7 +16712,7 @@
       <c r="Y512" s="1"/>
       <c r="Z512" s="1"/>
     </row>
-    <row r="513" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -16594,7 +16740,7 @@
       <c r="Y513" s="1"/>
       <c r="Z513" s="1"/>
     </row>
-    <row r="514" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -16622,7 +16768,7 @@
       <c r="Y514" s="1"/>
       <c r="Z514" s="1"/>
     </row>
-    <row r="515" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -16650,7 +16796,7 @@
       <c r="Y515" s="1"/>
       <c r="Z515" s="1"/>
     </row>
-    <row r="516" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -16678,7 +16824,7 @@
       <c r="Y516" s="1"/>
       <c r="Z516" s="1"/>
     </row>
-    <row r="517" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -16706,7 +16852,7 @@
       <c r="Y517" s="1"/>
       <c r="Z517" s="1"/>
     </row>
-    <row r="518" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -16734,7 +16880,7 @@
       <c r="Y518" s="1"/>
       <c r="Z518" s="1"/>
     </row>
-    <row r="519" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -16762,7 +16908,7 @@
       <c r="Y519" s="1"/>
       <c r="Z519" s="1"/>
     </row>
-    <row r="520" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -16790,7 +16936,7 @@
       <c r="Y520" s="1"/>
       <c r="Z520" s="1"/>
     </row>
-    <row r="521" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -16818,7 +16964,7 @@
       <c r="Y521" s="1"/>
       <c r="Z521" s="1"/>
     </row>
-    <row r="522" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -16846,7 +16992,7 @@
       <c r="Y522" s="1"/>
       <c r="Z522" s="1"/>
     </row>
-    <row r="523" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -16874,7 +17020,7 @@
       <c r="Y523" s="1"/>
       <c r="Z523" s="1"/>
     </row>
-    <row r="524" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -16902,7 +17048,7 @@
       <c r="Y524" s="1"/>
       <c r="Z524" s="1"/>
     </row>
-    <row r="525" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -16930,7 +17076,7 @@
       <c r="Y525" s="1"/>
       <c r="Z525" s="1"/>
     </row>
-    <row r="526" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -16958,7 +17104,7 @@
       <c r="Y526" s="1"/>
       <c r="Z526" s="1"/>
     </row>
-    <row r="527" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -16986,7 +17132,7 @@
       <c r="Y527" s="1"/>
       <c r="Z527" s="1"/>
     </row>
-    <row r="528" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -17014,7 +17160,7 @@
       <c r="Y528" s="1"/>
       <c r="Z528" s="1"/>
     </row>
-    <row r="529" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -17042,7 +17188,7 @@
       <c r="Y529" s="1"/>
       <c r="Z529" s="1"/>
     </row>
-    <row r="530" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -17070,7 +17216,7 @@
       <c r="Y530" s="1"/>
       <c r="Z530" s="1"/>
     </row>
-    <row r="531" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -17098,7 +17244,7 @@
       <c r="Y531" s="1"/>
       <c r="Z531" s="1"/>
     </row>
-    <row r="532" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -17126,7 +17272,7 @@
       <c r="Y532" s="1"/>
       <c r="Z532" s="1"/>
     </row>
-    <row r="533" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -17154,7 +17300,7 @@
       <c r="Y533" s="1"/>
       <c r="Z533" s="1"/>
     </row>
-    <row r="534" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -17182,7 +17328,7 @@
       <c r="Y534" s="1"/>
       <c r="Z534" s="1"/>
     </row>
-    <row r="535" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -17210,7 +17356,7 @@
       <c r="Y535" s="1"/>
       <c r="Z535" s="1"/>
     </row>
-    <row r="536" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17238,7 +17384,7 @@
       <c r="Y536" s="1"/>
       <c r="Z536" s="1"/>
     </row>
-    <row r="537" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17266,7 +17412,7 @@
       <c r="Y537" s="1"/>
       <c r="Z537" s="1"/>
     </row>
-    <row r="538" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17294,7 +17440,7 @@
       <c r="Y538" s="1"/>
       <c r="Z538" s="1"/>
     </row>
-    <row r="539" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17322,7 +17468,7 @@
       <c r="Y539" s="1"/>
       <c r="Z539" s="1"/>
     </row>
-    <row r="540" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17350,7 +17496,7 @@
       <c r="Y540" s="1"/>
       <c r="Z540" s="1"/>
     </row>
-    <row r="541" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17378,7 +17524,7 @@
       <c r="Y541" s="1"/>
       <c r="Z541" s="1"/>
     </row>
-    <row r="542" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17406,469 +17552,474 @@
       <c r="Y542" s="1"/>
       <c r="Z542" s="1"/>
     </row>
-    <row r="543" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="A73:C73"/>
     <mergeCell ref="A300:C300"/>
@@ -17881,11 +18032,6 @@
     <mergeCell ref="A144:C144"/>
     <mergeCell ref="A272:C272"/>
     <mergeCell ref="A286:C286"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A45:C45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
